--- a/docs/package/05_Delivery/Upload_Templates/GoLive_Migration_Workbook.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/GoLive_Migration_Workbook.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="301">
   <si>
     <t xml:space="preserve">Item</t>
   </si>
@@ -43,7 +43,7 @@
     <t xml:space="preserve">Cutover date</t>
   </si>
   <si>
-    <t xml:space="preserve">Not set yet: golive.cutover_date (Settings sheet of the configuration workbook, or Master &gt; Configuration)</t>
+    <t xml:space="preserve">2026-10-04 (setting golive.cutover_date)</t>
   </si>
   <si>
     <t xml:space="preserve">How to fill in</t>
@@ -160,7 +160,7 @@
     <t xml:space="preserve">Opening balances</t>
   </si>
   <si>
-    <t xml:space="preserve">The trial balance of the old system at the close of the day before the cutover date. Debits must equal credits; the sheet loads all or nothing; loading again replaces the earlier load. The fiscal year must have no journal posted before the cutover.</t>
+    <t xml:space="preserve">The trial balance of the old system at the close of the day before the cutover date. Debits must equal credits; the sheet loads all or nothing: when a row is in error, that row shows its error and the other rows are held (not loaded) until it is fixed; upload the whole sheet again. A row with no debit and no credit (zero balance) is accepted and ignored. Loading again replaces the earlier load. The fiscal year must have no journal posted before the cutover.</t>
   </si>
   <si>
     <t xml:space="preserve">Go-live lock</t>
@@ -187,7 +187,7 @@
     <t xml:space="preserve">Legacy numbers</t>
   </si>
   <si>
-    <t xml:space="preserve">Migrated records keep the numbers of the old system (client code, policy number, claim number). New business takes the next number of its Document Numbering series (Numbering sheet of the configuration workbook); a legacy number in the range a series has still to issue is refused.</t>
+    <t xml:space="preserve">Migrated records keep the numbers of the old system (client code, policy number, claim number, and the bill number of an open item). New business takes the next number of its Document Numbering series (Numbering sheet of the configuration workbook); a legacy number in the range a series has still to issue is refused. An open item whose bill number another bill already carries (one debit note over several policies) gets the next invoice number and keeps the old number as its reference, shown next to the bill number and searchable.</t>
   </si>
   <si>
     <t xml:space="preserve">Transactions</t>
@@ -439,7 +439,7 @@
     <t xml:space="preserve">Open Items: Bill Reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Required. Invoice or debit note number in the old system; one per policy</t>
+    <t xml:space="preserve">Required. Invoice or debit note number in the old system; one per policy. Kept as the bill number in BrokerVerse</t>
   </si>
   <si>
     <t xml:space="preserve">Open Items: Due Date</t>
@@ -526,7 +526,7 @@
     <t xml:space="preserve">Opening Balances: Debit</t>
   </si>
   <si>
-    <t xml:space="preserve">Optional. Amount in PHP, no sign; the account balance when it is a debit balance</t>
+    <t xml:space="preserve">Optional. Amount in PHP, no sign; the account balance when it is a debit balance. A row with no debit and no credit (zero balance) is ignored</t>
   </si>
   <si>
     <t xml:space="preserve">Opening Balances: Credit</t>
@@ -565,79 +565,100 @@
     <t xml:space="preserve">registered</t>
   </si>
   <si>
+    <t xml:space="preserve">ARC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">corporate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">direct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviewing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in-review</t>
+  </si>
+  <si>
     <t xml:space="preserve">FPG</t>
   </si>
   <si>
-    <t xml:space="preserve">BOND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">corporate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">direct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reviewing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">in-review</t>
+    <t xml:space="preserve">BURGLARY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CGL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refunded</t>
   </si>
   <si>
     <t xml:space="preserve">MALAYAN</t>
   </si>
   <si>
-    <t xml:space="preserve">BURGLARY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partial</t>
+    <t xml:space="preserve">CTPL</t>
   </si>
   <si>
     <t xml:space="preserve">MAPFRE</t>
   </si>
   <si>
-    <t xml:space="preserve">CAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Completed</t>
+    <t xml:space="preserve">EAR</t>
   </si>
   <si>
     <t xml:space="preserve">MERCANTILE</t>
   </si>
   <si>
-    <t xml:space="preserve">CGL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Refunded</t>
+    <t xml:space="preserve">EB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPA</t>
   </si>
   <si>
     <t xml:space="preserve">PIONEER</t>
   </si>
   <si>
-    <t xml:space="preserve">CTPL</t>
+    <t xml:space="preserve">HOME</t>
   </si>
   <si>
     <t xml:space="preserve">STANDARD</t>
   </si>
   <si>
-    <t xml:space="preserve">EAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOME</t>
-  </si>
-  <si>
     <t xml:space="preserve">HULL</t>
   </si>
   <si>
+    <t xml:space="preserve">TALA</t>
+  </si>
+  <si>
     <t xml:space="preserve">IAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIS</t>
   </si>
   <si>
     <t xml:space="preserve">MARINE</t>
@@ -1915,9 +1936,11 @@
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
+      <c r="E8" s="11" t="s">
+        <v>201</v>
+      </c>
       <c r="F8" s="11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9">
@@ -1925,9 +1948,11 @@
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
+      <c r="E9" s="11" t="s">
+        <v>203</v>
+      </c>
       <c r="F9" s="11" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10">
@@ -1935,9 +1960,11 @@
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
+      <c r="E10" s="11" t="s">
+        <v>205</v>
+      </c>
       <c r="F10" s="11" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11">
@@ -1945,9 +1972,11 @@
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
+      <c r="E11" s="11" t="s">
+        <v>207</v>
+      </c>
       <c r="F11" s="11" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1955,9 +1984,11 @@
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
+      <c r="E12" s="11" t="s">
+        <v>209</v>
+      </c>
       <c r="F12" s="11" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13">
@@ -1965,9 +1996,11 @@
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
+      <c r="E13" s="11" t="s">
+        <v>211</v>
+      </c>
       <c r="F13" s="11" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14">
@@ -1975,9 +2008,11 @@
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
+      <c r="E14" s="11" t="s">
+        <v>213</v>
+      </c>
       <c r="F14" s="11" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15">
@@ -1987,7 +2022,7 @@
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16">
@@ -1997,7 +2032,7 @@
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17">
@@ -2007,7 +2042,7 @@
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18">
@@ -2017,7 +2052,7 @@
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19">
@@ -2027,7 +2062,7 @@
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20">
@@ -2037,7 +2072,7 @@
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -2069,92 +2104,92 @@
   <sheetData>
     <row r="1" spans="1:15" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>178</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="9" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -2192,40 +2227,40 @@
   <sheetData>
     <row r="1" spans="1:16" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="M1" s="8" t="s">
         <v>173</v>
@@ -2234,43 +2269,43 @@
         <v>174</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
@@ -2280,14 +2315,14 @@
         <v>193</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="P2" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="C2:C5000">
-      <formula1>Lists!$E$2:$E$7</formula1>
+      <formula1>Lists!$E$2:$E$14</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="D2:D5000">
       <formula1>Lists!$F$2:$F$20</formula1>
@@ -2317,36 +2352,36 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C2" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>261</v>
-      </c>
       <c r="E2" s="9" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -2373,63 +2408,63 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>187</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="J2" s="9"/>
     </row>
@@ -2456,27 +2491,27 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="D2" s="9"/>
     </row>

--- a/docs/package/05_Delivery/Upload_Templates/GoLive_Migration_Workbook.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/GoLive_Migration_Workbook.xlsx
@@ -43,7 +43,7 @@
     <t xml:space="preserve">Cutover date</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 (setting golive.cutover_date)</t>
+    <t xml:space="preserve">Not set yet: golive.cutover_date (Settings sheet of the configuration workbook, or Master &gt; Configuration)</t>
   </si>
   <si>
     <t xml:space="preserve">How to fill in</t>
@@ -565,7 +565,7 @@
     <t xml:space="preserve">registered</t>
   </si>
   <si>
-    <t xml:space="preserve">ARC</t>
+    <t xml:space="preserve">APEX</t>
   </si>
   <si>
     <t xml:space="preserve">BOND</t>
@@ -583,25 +583,25 @@
     <t xml:space="preserve">in-review</t>
   </si>
   <si>
+    <t xml:space="preserve">EVERSAFE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BURGLARY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial</t>
+  </si>
+  <si>
     <t xml:space="preserve">FPG</t>
   </si>
   <si>
-    <t xml:space="preserve">BURGLARY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HAR</t>
-  </si>
-  <si>
     <t xml:space="preserve">CAR</t>
   </si>
   <si>
     <t xml:space="preserve">Completed</t>
   </si>
   <si>
-    <t xml:space="preserve">LUZ</t>
+    <t xml:space="preserve">GOLDENHORIZON</t>
   </si>
   <si>
     <t xml:space="preserve">CGL</t>
@@ -610,33 +610,33 @@
     <t xml:space="preserve">Refunded</t>
   </si>
   <si>
+    <t xml:space="preserve">INTEGRITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIBERTYSHIELD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EAR</t>
+  </si>
+  <si>
     <t xml:space="preserve">MALAYAN</t>
   </si>
   <si>
-    <t xml:space="preserve">CTPL</t>
+    <t xml:space="preserve">EB</t>
   </si>
   <si>
     <t xml:space="preserve">MAPFRE</t>
   </si>
   <si>
-    <t xml:space="preserve">EAR</t>
+    <t xml:space="preserve">FIRE</t>
   </si>
   <si>
     <t xml:space="preserve">MERCANTILE</t>
   </si>
   <si>
-    <t xml:space="preserve">EB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCIC</t>
-  </si>
-  <si>
     <t xml:space="preserve">GPA</t>
   </si>
   <si>
@@ -646,19 +646,19 @@
     <t xml:space="preserve">HOME</t>
   </si>
   <si>
+    <t xml:space="preserve">SECUREGUARD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HULL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SENTINEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAR</t>
+  </si>
+  <si>
     <t xml:space="preserve">STANDARD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HULL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TALA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VIS</t>
   </si>
   <si>
     <t xml:space="preserve">MARINE</t>
@@ -2283,7 +2283,7 @@
         <v>262</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>218</v>

--- a/docs/package/05_Delivery/Upload_Templates/GoLive_Migration_Workbook.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/GoLive_Migration_Workbook.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="309">
   <si>
     <t xml:space="preserve">Item</t>
   </si>
@@ -316,22 +316,34 @@
     <t xml:space="preserve">Clients: Address</t>
   </si>
   <si>
-    <t xml:space="preserve">Optional. Street address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clients: City</t>
+    <t xml:space="preserve">Optional. House / unit no. and street</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clients: Barangay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clients: City / Municipality</t>
   </si>
   <si>
     <t xml:space="preserve">Clients: Province</t>
   </si>
   <si>
+    <t xml:space="preserve">Optional. Province of the Province master (Metro Manila for NCR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clients: Region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Filled from the province when empty</t>
+  </si>
+  <si>
     <t xml:space="preserve">Clients: Country</t>
   </si>
   <si>
     <t xml:space="preserve">Optional. Philippines when empty</t>
   </si>
   <si>
-    <t xml:space="preserve">Clients: Postal Code</t>
+    <t xml:space="preserve">Clients: ZIP Code</t>
   </si>
   <si>
     <t xml:space="preserve">Policies: Policy Number</t>
@@ -715,16 +727,22 @@
     <t xml:space="preserve">Address</t>
   </si>
   <si>
-    <t xml:space="preserve">City</t>
+    <t xml:space="preserve">Barangay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">City / Municipality</t>
   </si>
   <si>
     <t xml:space="preserve">Province</t>
   </si>
   <si>
+    <t xml:space="preserve">Region</t>
+  </si>
+  <si>
     <t xml:space="preserve">Country</t>
   </si>
   <si>
-    <t xml:space="preserve">Postal Code</t>
+    <t xml:space="preserve">ZIP Code</t>
   </si>
   <si>
     <t xml:space="preserve">SAMPLE C-000123</t>
@@ -748,13 +766,19 @@
     <t xml:space="preserve">1988-04-12</t>
   </si>
   <si>
-    <t xml:space="preserve">12 Mabini St., San Antonio</t>
+    <t xml:space="preserve">Unit 4B, 12 Mabini St.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Antonio</t>
   </si>
   <si>
     <t xml:space="preserve">Pasig City</t>
   </si>
   <si>
     <t xml:space="preserve">Metro Manila</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National Capital Region (NCR)</t>
   </si>
   <si>
     <t xml:space="preserve">Philippines</t>
@@ -1048,7 +1072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B95"/>
+  <dimension ref="A1:B97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -1516,23 +1540,23 @@
         <v>104</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
     </row>
     <row r="63">
@@ -1708,23 +1732,23 @@
         <v>151</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
     </row>
     <row r="87">
@@ -1740,20 +1764,20 @@
         <v>158</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>91</v>
+        <v>159</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>91</v>
@@ -1761,18 +1785,18 @@
     </row>
     <row r="91">
       <c r="A91" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>165</v>
+        <v>91</v>
       </c>
     </row>
     <row r="93">
@@ -1797,6 +1821,22 @@
       </c>
       <c r="B95" s="4" t="s">
         <v>171</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="s">
+        <v>174</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -1819,104 +1859,104 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="11" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
       <c r="C5" s="11" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="11" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="11" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7">
@@ -1925,10 +1965,10 @@
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
       <c r="E7" s="11" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8">
@@ -1937,10 +1977,10 @@
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
       <c r="E8" s="11" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9">
@@ -1949,10 +1989,10 @@
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10">
@@ -1961,10 +2001,10 @@
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -1973,10 +2013,10 @@
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
       <c r="E11" s="11" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -1985,10 +2025,10 @@
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
       <c r="E12" s="11" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13">
@@ -1997,10 +2037,10 @@
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
       <c r="E13" s="11" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14">
@@ -2009,10 +2049,10 @@
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
       <c r="E14" s="11" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="15">
@@ -2022,7 +2062,7 @@
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16">
@@ -2032,7 +2072,7 @@
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17">
@@ -2042,7 +2082,7 @@
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18">
@@ -2052,7 +2092,7 @@
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19">
@@ -2062,7 +2102,7 @@
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20">
@@ -2072,7 +2112,7 @@
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -2082,7 +2122,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17" style="11" customWidth="1"/>
@@ -2097,99 +2137,113 @@
     <col min="10" max="10" width="14" style="11" customWidth="1"/>
     <col min="11" max="11" width="14" style="11" customWidth="1"/>
     <col min="12" max="12" width="14" style="11" customWidth="1"/>
-    <col min="13" max="13" width="14" style="11" customWidth="1"/>
+    <col min="13" max="13" width="25" style="11" customWidth="1"/>
     <col min="14" max="14" width="14" style="11" customWidth="1"/>
-    <col min="15" max="15" width="17" style="11" customWidth="1"/>
+    <col min="15" max="15" width="14" style="11" customWidth="1"/>
+    <col min="16" max="16" width="14" style="11" customWidth="1"/>
+    <col min="17" max="17" width="14" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="20" customHeight="1">
+    <row r="1" spans="1:17" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>235</v>
+        <v>239</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="9" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>247</v>
+        <v>253</v>
+      </c>
+      <c r="P2" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q2" s="9" t="s">
+        <v>255</v>
       </c>
     </row>
   </sheetData>
@@ -2227,95 +2281,95 @@
   <sheetData>
     <row r="1" spans="1:16" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="P2" s="9"/>
     </row>
@@ -2352,36 +2406,36 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -2408,63 +2462,63 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="J2" s="9"/>
     </row>
@@ -2491,27 +2545,27 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="D2" s="9"/>
     </row>

--- a/docs/package/05_Delivery/Upload_Templates/GoLive_Migration_Workbook.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/GoLive_Migration_Workbook.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="301">
   <si>
     <t xml:space="preserve">Item</t>
   </si>
@@ -34,10 +34,10 @@
     <t xml:space="preserve">Blank template: fill in the object sheets.</t>
   </si>
   <si>
-    <t xml:space="preserve">Upload on</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master &gt; Go-Live Data Load (System Administrator). API: POST /api/data-load/batches (multipart field "file", field kit).</t>
+    <t xml:space="preserve">Upload with</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API: POST /api/data-load/batches (multipart field "file", field kit), System Administrator; the go-live scripts (npm run rehearsal:golive) use it.</t>
   </si>
   <si>
     <t xml:space="preserve">Cutover date</t>
@@ -580,7 +580,7 @@
     <t xml:space="preserve">APEX</t>
   </si>
   <si>
-    <t xml:space="preserve">BOND</t>
+    <t xml:space="preserve">CL-COMP</t>
   </si>
   <si>
     <t xml:space="preserve">corporate</t>
@@ -595,103 +595,79 @@
     <t xml:space="preserve">in-review</t>
   </si>
   <si>
+    <t xml:space="preserve">AXA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CL-VOL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial</t>
+  </si>
+  <si>
     <t xml:space="preserve">EVERSAFE</t>
   </si>
   <si>
-    <t xml:space="preserve">BURGLARY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partial</t>
+    <t xml:space="preserve">CTPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completed</t>
   </si>
   <si>
     <t xml:space="preserve">FPG</t>
   </si>
   <si>
-    <t xml:space="preserve">CAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Completed</t>
+    <t xml:space="preserve">GPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refunded</t>
   </si>
   <si>
     <t xml:space="preserve">GOLDENHORIZON</t>
   </si>
   <si>
-    <t xml:space="preserve">CGL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Refunded</t>
+    <t xml:space="preserve">MOTOR</t>
   </si>
   <si>
     <t xml:space="preserve">INTEGRITY</t>
   </si>
   <si>
-    <t xml:space="preserve">CTPL</t>
+    <t xml:space="preserve">PA</t>
   </si>
   <si>
     <t xml:space="preserve">LIBERTYSHIELD</t>
   </si>
   <si>
-    <t xml:space="preserve">EAR</t>
+    <t xml:space="preserve">PARCEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAAGAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRAVEL</t>
   </si>
   <si>
     <t xml:space="preserve">MALAYAN</t>
   </si>
   <si>
-    <t xml:space="preserve">EB</t>
-  </si>
-  <si>
     <t xml:space="preserve">MAPFRE</t>
   </si>
   <si>
-    <t xml:space="preserve">FIRE</t>
-  </si>
-  <si>
     <t xml:space="preserve">MERCANTILE</t>
   </si>
   <si>
-    <t xml:space="preserve">GPA</t>
-  </si>
-  <si>
     <t xml:space="preserve">PIONEER</t>
   </si>
   <si>
-    <t xml:space="preserve">HOME</t>
-  </si>
-  <si>
     <t xml:space="preserve">SECUREGUARD</t>
   </si>
   <si>
-    <t xml:space="preserve">HULL</t>
-  </si>
-  <si>
     <t xml:space="preserve">SENTINEL</t>
   </si>
   <si>
-    <t xml:space="preserve">IAR</t>
-  </si>
-  <si>
     <t xml:space="preserve">STANDARD</t>
   </si>
   <si>
-    <t xml:space="preserve">MARINE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MICRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MONEY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOTOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRAVEL</t>
+    <t xml:space="preserve">STRONGHOLD</t>
   </si>
   <si>
     <t xml:space="preserve">Client Code *</t>
@@ -953,7 +929,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -980,8 +956,42 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0B2A4A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF5F6B76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1009,6 +1019,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF4CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1040,9 +1068,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1063,6 +1091,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1846,7 +1881,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" style="11" customWidth="1"/>
@@ -2003,9 +2038,7 @@
       <c r="E10" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>210</v>
-      </c>
+      <c r="F10" s="11"/>
     </row>
     <row r="11">
       <c r="A11" s="11"/>
@@ -2013,11 +2046,9 @@
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
       <c r="E11" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>212</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="F11" s="11"/>
     </row>
     <row r="12">
       <c r="A12" s="11"/>
@@ -2025,11 +2056,9 @@
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
       <c r="E12" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>214</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="F12" s="11"/>
     </row>
     <row r="13">
       <c r="A13" s="11"/>
@@ -2037,11 +2066,9 @@
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
       <c r="E13" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>216</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="F13" s="11"/>
     </row>
     <row r="14">
       <c r="A14" s="11"/>
@@ -2049,71 +2076,39 @@
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
       <c r="E14" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>218</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="F14" s="11"/>
     </row>
     <row r="15">
       <c r="A15" s="11"/>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11" t="s">
-        <v>219</v>
-      </c>
+      <c r="E15" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="F15" s="11"/>
     </row>
     <row r="16">
       <c r="A16" s="11"/>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11" t="s">
-        <v>220</v>
-      </c>
+      <c r="E16" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="F16" s="11"/>
     </row>
     <row r="17">
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11" t="s">
-        <v>224</v>
-      </c>
+      <c r="E17" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="F17" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2146,104 +2141,104 @@
   <sheetData>
     <row r="1" spans="1:17" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>233</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="P1" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>182</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="9" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -2281,40 +2276,40 @@
   <sheetData>
     <row r="1" spans="1:16" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>258</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>266</v>
       </c>
       <c r="M1" s="8" t="s">
         <v>177</v>
@@ -2323,43 +2318,43 @@
         <v>178</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
@@ -2369,17 +2364,17 @@
         <v>197</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="P2" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="C2:C5000">
-      <formula1>Lists!$E$2:$E$14</formula1>
+      <formula1>Lists!$E$2:$E$17</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="D2:D5000">
-      <formula1>Lists!$F$2:$F$20</formula1>
+      <formula1>Lists!$F$2:$F$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="M2:M5000">
       <formula1>Lists!$B$2:$B$3</formula1>
@@ -2406,36 +2401,36 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="D2" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -2462,63 +2457,63 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>285</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>191</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="J2" s="9"/>
     </row>
@@ -2545,27 +2540,27 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="D2" s="9"/>
     </row>

--- a/docs/package/05_Delivery/Upload_Templates/GoLive_Migration_Workbook.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/GoLive_Migration_Workbook.xlsx
@@ -8,16 +8,24 @@
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Lists" sheetId="2" r:id="rId2"/>
     <sheet name="Clients" sheetId="3" r:id="rId3"/>
-    <sheet name="Policies" sheetId="4" r:id="rId4"/>
-    <sheet name="Open Items" sheetId="5" r:id="rId5"/>
-    <sheet name="Open Claims" sheetId="6" r:id="rId6"/>
-    <sheet name="Opening Balances" sheetId="7" r:id="rId7"/>
+    <sheet name="Policies - Motor" sheetId="4" r:id="rId4"/>
+    <sheet name="Policies - CTPL" sheetId="5" r:id="rId5"/>
+    <sheet name="Policies - Personal Accident" sheetId="6" r:id="rId6"/>
+    <sheet name="Policies - Credit Life" sheetId="7" r:id="rId7"/>
+    <sheet name="Policies - Travel" sheetId="8" r:id="rId8"/>
+    <sheet name="Policies - Other Lines" sheetId="9" r:id="rId9"/>
+    <sheet name="Open Items" sheetId="10" r:id="rId10"/>
+    <sheet name="Post-Dated Cheques" sheetId="11" r:id="rId11"/>
+    <sheet name="Open Claims" sheetId="12" r:id="rId12"/>
+    <sheet name="Opening Balances" sheetId="13" r:id="rId13"/>
+    <sheet name="Control Totals" sheetId="14" r:id="rId14"/>
+    <sheet name="Control" sheetId="15" state="hidden" r:id="rId15"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1125" uniqueCount="774">
   <si>
     <t xml:space="preserve">Item</t>
   </si>
@@ -34,16 +42,16 @@
     <t xml:space="preserve">Blank template: fill in the object sheets.</t>
   </si>
   <si>
-    <t xml:space="preserve">Upload with</t>
-  </si>
-  <si>
-    <t xml:space="preserve">API: POST /api/data-load/batches (multipart field "file", field kit), System Administrator; the go-live scripts (npm run rehearsal:golive) use it.</t>
+    <t xml:space="preserve">Upload</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master &gt; System Configuration &gt; Data Migration &amp; Go-Live &gt; Loads: upload, review the result of each row, then submit the load for approval.</t>
   </si>
   <si>
     <t xml:space="preserve">Cutover date</t>
   </si>
   <si>
-    <t xml:space="preserve">Not set yet: golive.cutover_date (Settings sheet of the configuration workbook, or Master &gt; Configuration)</t>
+    <t xml:space="preserve">Not set yet: set it on Data Migration &amp; Go-Live &gt; Go-Live before the migration workbook is validated.</t>
   </si>
   <si>
     <t xml:space="preserve">How to fill in</t>
@@ -70,7 +78,7 @@
     <t xml:space="preserve">Formats</t>
   </si>
   <si>
-    <t xml:space="preserve">Dates as YYYY-MM-DD; amounts as plain numbers (no currency sign); rates as fractions where the column says so (0.20 for 20%). The sheets are formatted as text so Excel keeps codes and dates as typed.</t>
+    <t xml:space="preserve">Dates as YYYY-MM-DD; amounts as plain numbers (no currency sign) with at most two decimals; rates as fractions where the column says so (0.20 for 20%). The sheets are formatted as text so Excel keeps codes and dates as typed.</t>
   </si>
   <si>
     <t xml:space="preserve">Keys</t>
@@ -79,6 +87,18 @@
     <t xml:space="preserve">Every row is matched on its natural key (code, username, setting key, legacy number ...): a row whose key exists updates that record, a new key creates one. Loading the same or a corrected workbook again never duplicates; unchanged rows are skipped.</t>
   </si>
   <si>
+    <t xml:space="preserve">Hidden values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A cell shown masked (with **) keeps the value stored in BrokerVerse; a masked TIN, birth date or key is refused: enter the full value.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The hidden Control sheet identifies this file (kit, sheets, layout). Do not remove it; a file of another kit or of an older layout is refused: download the template again.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Load order</t>
   </si>
   <si>
@@ -88,31 +108,58 @@
     <t xml:space="preserve">Operations &gt; Clients. Key: Client Code</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Policies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations &gt; Policy. Key: Policy Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Open Items</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accounts &gt; Collections. Key: Policy Number + Bill Reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Open Claims</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations &gt; Claims. Key: Claim Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Opening Balances</t>
+    <t xml:space="preserve">2. Policies - Motor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations &gt; Policy. Key: Policy Number. After: Clients</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Policies - CTPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Policies - Personal Accident</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Policies - Credit Life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Policies - Travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Policies - Other Lines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. Open Items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accounts &gt; Collections. Key: Policy Number + Bill Reference. After: Policies - Motor, Policies - CTPL, Policies - Personal Accident, Policies - Credit Life, Policies - Travel, Policies - Other Lines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. Post-Dated Cheques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accounts &gt; Post-Dated Cheques. Key: Drawee Bank + Cheque Number. After: Open Items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10. Open Claims</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations &gt; Claims. Key: Claim Number. After: Policies - Motor, Policies - CTPL, Policies - Personal Accident, Policies - Credit Life, Policies - Travel, Policies - Other Lines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11. Opening Balances</t>
   </si>
   <si>
     <t xml:space="preserve">Accounts &gt; Period End &gt; Period Management (opening balances). Key: Account Code</t>
   </si>
   <si>
-    <t xml:space="preserve">Validate, fix and load</t>
+    <t xml:space="preserve">12. Control Totals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Migration &amp; Go-Live &gt; Reconciliation. Key: Object + Measure + Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate, review and load</t>
   </si>
   <si>
     <t xml:space="preserve">1. Upload and validate</t>
@@ -121,40 +168,46 @@
     <t xml:space="preserve">The upload validates without saving: every sheet runs through its importer in the load order above inside one database transaction that is rolled back, so a row may refer to a record of an earlier sheet of the same workbook (e.g. a policy to a client and an insurer).</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Result</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rows read, valid and with errors per sheet; each error with its sheet, row number, column and message.</t>
+    <t xml:space="preserve">2. Result of each row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New: the key is not in BrokerVerse, the row creates a record. Changed: the key is stored with other values; the review shows each changed column, old -&gt; new. Unchanged: equal to the stored record, nothing to load. Duplicate: the row would create a record that matches another record (below); it loads only once resolved. Error: a check failed (column and message).</t>
   </si>
   <si>
     <t xml:space="preserve">3. Fix</t>
   </si>
   <si>
-    <t xml:space="preserve">Download errors: a workbook in this layout with only the rows in error and an Errors column. Correct those rows and upload that file (or the whole corrected workbook) again.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Load</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load runs when the latest validation has no error (or with "load valid rows only"). Everything is loaded in one transaction, recorded in the history and the audit trail.</t>
+    <t xml:space="preserve">Download errors: a workbook in this layout with the rows in error and the unresolved duplicates and an Errors column. Correct those rows and upload that file (or the whole corrected workbook) again.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Duplicates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolve each duplicate on the review: Load as new (a reason is kept), Use existing (the row creates nothing and the legacy value is mapped to the existing record for every later load), or, for a policy number of another insurer, Load with insurer suffix (number/INSURER CODE). Or fix the file.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Load</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load runs when the latest validation has no error and no unresolved duplicate. Everything is loaded in one transaction, recorded in the load history and in the history of each record.</t>
   </si>
   <si>
     <t xml:space="preserve">Cutover date rule</t>
   </si>
   <si>
-    <t xml:space="preserve">golive.cutover_date is the first day of live transactions in BrokerVerse. It must be set before the migration workbook is validated.</t>
+    <t xml:space="preserve">The cutover date is the first day of live transactions in BrokerVerse. It must be set before the migration workbook is validated.</t>
   </si>
   <si>
     <t xml:space="preserve">Dated before cutover</t>
   </si>
   <si>
-    <t xml:space="preserve">Policy issue dates, claim loss and reported dates and client birth dates must be before the cutover date; a row dated on or after it is refused (enter it in BrokerVerse as new business).</t>
+    <t xml:space="preserve">Policy issue dates, claim loss and reported dates, cheque received dates and client birth dates must be before the cutover date; a row dated on or after it is refused (enter it in BrokerVerse as new business).</t>
   </si>
   <si>
     <t xml:space="preserve">In force</t>
   </si>
   <si>
-    <t xml:space="preserve">Policies must still be in force at cutover (expiry on or after the cutover date). Open claims are registered or in review.</t>
+    <t xml:space="preserve">Policies must still be in force at cutover (expiry on or after the cutover date). Open claims are registered or in review. Post-dated cheques are on hand, dated on or after the cutover date.</t>
   </si>
   <si>
     <t xml:space="preserve">Opening balances</t>
@@ -166,28 +219,136 @@
     <t xml:space="preserve">Go-live lock</t>
   </si>
   <si>
-    <t xml:space="preserve">Once golive.locked is on (Master &gt; Configuration), the migration workbook is refused; the configuration workbook stays available for new masters.</t>
+    <t xml:space="preserve">Once go-live is locked, the migration workbook is refused; the configuration workbook stays available for new masters.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policy sheets per product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Products: MOTOR. Columns: Plate Number, Conduction Sticker, Chassis Number, Engine Number, MV File Number, Brand, Model, Variant, Model Year, Body Type, Colour, Seating Capacity, Mortgagee / Financier, TFS Loan Reference, Dealer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Products: CTPL. Columns: Plate Number, Conduction Sticker, Chassis Number, Engine Number, MV File Number, COC Number, Authentication Code, Vehicle Type, Brand, Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Products: GPA, PA. Columns: Plan, Insured Persons, Beneficiary / Nominee, Occupation Class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Products: CL-COMP, CL-VOL. Columns: Borrower Name, TFS Loan Account Number, Loan Amount, Loan Term in Months, Loan Release Date, Financier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Products: TRAVEL. Columns: Plan / Policy Type, Destination, Travel Start, Travel End, Travellers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Other Lines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Products: PARCEL. Columns: common columns only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One policy number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A policy number is on one sheet only. The single Policies sheet of the earlier layout is still read, for any product.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amounts and currency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amounts are pesos as booked in the legacy ledger, at most two decimals (never rounded on loading, so the workbook and BrokerVerse totals agree to the centavo). A foreign-currency policy keeps its Original Currency, Original Sum Insured and Exchange Rate as reference. Open items are in PHP only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTPL certificates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A migrated CTPL policy records its COC as authenticated (manual, not sent to the LTO): the same COC can never be issued again.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duplicate checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same TIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clients: a TIN already held by another client, in the file or in BrokerVerse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same name and birth date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Individual clients: the same first and last name (Jr, Sr, II, III set aside) and the same birth date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same company name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corporate clients: the same company name once punctuation and Inc, Corp, Co, Ltd, OPC, Phils are set aside, when one of them has no TIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same vehicle in force</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motor and CTPL: the same plate, conduction sticker or chassis number on another policy of the same sheet in force over the same period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same COC number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTPL: the same COC number of the same insurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policy number of another insurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A policy number that a policy of another insurer carries (the same insurer is an error)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurer name variant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An insurer written another way (Malayan Ins. Co., Inc.): use the existing insurer, the spelling is then mapped for later loads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configuration masters: a new record with the same name as an existing one</t>
   </si>
   <si>
     <t xml:space="preserve">New and migrated data</t>
   </si>
   <si>
-    <t xml:space="preserve">Flags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migrated clients and policies carry source go-live-migration (policy: doc.source) and the load batch id; open items are bills with source opening and the cutover date; open claims carry details.source go-live-migration.</t>
+    <t xml:space="preserve">Origin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every migrated record is marked Migrated with the legacy system, its legacy number, when and by whom it was migrated and the load (MIG-000012); records entered after go-live are Issued in BrokerVerse. Older flags stay for the reports that read them: source go-live-migration on clients, policies and claims, source opening on open items.</t>
   </si>
   <si>
     <t xml:space="preserve">No postings</t>
   </si>
   <si>
-    <t xml:space="preserve">Migration posts no journal, bill booking or commission accrual: the opening balances carry the money. Open items age and are collected with normal official receipts.</t>
+    <t xml:space="preserve">Migration posts no journal, bill booking or commission accrual: the opening balances carry the money. Open items age and are collected with normal official receipts; a post-dated cheque deposited after go-live creates its receipt.</t>
   </si>
   <si>
     <t xml:space="preserve">Legacy numbers</t>
   </si>
   <si>
-    <t xml:space="preserve">Migrated records keep the numbers of the old system (client code, policy number, claim number, and the bill number of an open item). New business takes the next number of its Document Numbering series (Numbering sheet of the configuration workbook); a legacy number in the range a series has still to issue is refused. An open item whose bill number another bill already carries (one debit note over several policies) gets the next invoice number and keeps the old number as its reference, shown next to the bill number and searchable.</t>
+    <t xml:space="preserve">Migrated records keep the numbers of the old system (client code, policy number, claim number, and the bill number of an open item). New business takes the insurer's policy number or the next number of its Document Numbering series; a legacy number in the range a series has still to issue is refused. An open item whose bill number another bill already carries (one debit note over several policies) gets the next invoice number and keeps the old number as its reference, shown next to the bill number and searchable.</t>
   </si>
   <si>
     <t xml:space="preserve">Transactions</t>
@@ -199,19 +360,58 @@
     <t xml:space="preserve">Renewals</t>
   </si>
   <si>
-    <t xml:space="preserve">Migrated in-force policies are ordinary active policies: the renewal queue picks them up as they approach expiry. Policies expiring soon need no separate sheet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Policy lists and the API show the source (go-live-migration) and can be filtered on it (GET /api/policies?source=go-live-migration).</t>
+    <t xml:space="preserve">Migrated in-force policies are ordinary active policies: the renewal queue picks them up as they approach expiry, and the renewal carries the vehicle, loan and plan details of the migrated term. The renewal is business issued in BrokerVerse.</t>
   </si>
   <si>
     <t xml:space="preserve">Reconciliation</t>
   </si>
   <si>
-    <t xml:space="preserve">Every validation and load gives control totals per sheet (counts, gross premium, open balances, claim estimates, trial balance debits and credits) and the check premiums receivable control account = open items, to compare with the control totals of the old system. Download it from the history.</t>
+    <t xml:space="preserve">Enter the legacy figures on the Control Totals sheet (object, measure, group, value): they are compared with the workbook and with BrokerVerse after the load.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document file names</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Convention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;RecordType&gt;_&lt;RecordNumber&gt;_&lt;DocumentType&gt;_&lt;YYYYMMDD&gt;[_&lt;n&gt;].&lt;ext&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Record types</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLT client, POL policy, END endorsement, CLM claim, BIL bill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Record number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The legacy number as loaded (client code, policy number, claim number, bill reference), with / and spaces written as -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document types</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLSCH, COC, OR, ID, ORCR, LOAN, ENDT, CLAIMFORM, POLICE, PHOTO, ESTIMATE, OTHER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date and sequence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YYYYMMDD: the document date; _&lt;n&gt; when several files share the rest of the name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extensions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdf, jpg, jpeg, png, tif, tiff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POL_PC-MLY-2026-000101_POLSCH_20260225.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">Not in this workbook</t>
@@ -241,6 +441,18 @@
     <t xml:space="preserve">Not migrated: they stay in the old system (read only)</t>
   </si>
   <si>
+    <t xml:space="preserve">Cheques deposited in the legacy system but not cleared at cutover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stay on the legacy bank reconciliation; a bounce after go-live is a late legacy item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit balances and unapplied collections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part of the GL opening balances, with the legacy listing per client in the Control Totals sheet</t>
+  </si>
+  <si>
     <t xml:space="preserve">Leads and quotations in progress</t>
   </si>
   <si>
@@ -256,7 +468,7 @@
     <t xml:space="preserve">Documents and images of the old system</t>
   </si>
   <si>
-    <t xml:space="preserve">Attach on the policy or claim screen when needed</t>
+    <t xml:space="preserve">Named by the document file naming convention below and attached on the record screen when needed</t>
   </si>
   <si>
     <t xml:space="preserve">Columns</t>
@@ -346,100 +558,676 @@
     <t xml:space="preserve">Clients: ZIP Code</t>
   </si>
   <si>
-    <t xml:space="preserve">Policies: Policy Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Required. Policy number in the old system (insurer policy number); kept</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Policies: Client Code</t>
+    <t xml:space="preserve">Policies - Motor: Policy Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Policy number in the legacy system (the insurer policy number); kept as the policy number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Client Code</t>
   </si>
   <si>
     <t xml:space="preserve">Required. Client Code of the Clients sheet (or of a client already migrated)</t>
   </si>
   <si>
-    <t xml:space="preserve">Policies: Insurer</t>
+    <t xml:space="preserve">Policies - Motor: Insurer</t>
   </si>
   <si>
     <t xml:space="preserve">Required. Insurer code (or name) of the Insurance Company master. Values: Lists sheet, Insurers</t>
   </si>
   <si>
-    <t xml:space="preserve">Policies: Product</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Required. Product code (or name) of the Product master, e.g. MOTOR, FIRE. Values: Lists sheet, Products</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Policies: Insured Name</t>
+    <t xml:space="preserve">Policies - Motor: Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Product code of the Product master (Lists sheet: the products of this sheet). Values: Lists sheet, Products Motor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Insured Name</t>
   </si>
   <si>
     <t xml:space="preserve">Optional. The client name when empty</t>
   </si>
   <si>
-    <t xml:space="preserve">Policies: Inception Date</t>
+    <t xml:space="preserve">Policies - Motor: Inception Date</t>
   </si>
   <si>
     <t xml:space="preserve">Required. Date YYYY-MM-DD</t>
   </si>
   <si>
-    <t xml:space="preserve">Policies: Expiry Date</t>
+    <t xml:space="preserve">Policies - Motor: Expiry Date</t>
   </si>
   <si>
     <t xml:space="preserve">Required. Date YYYY-MM-DD, on or after the cutover date (in force)</t>
   </si>
   <si>
-    <t xml:space="preserve">Policies: Issue Date</t>
+    <t xml:space="preserve">Policies - Motor: Issue Date</t>
   </si>
   <si>
     <t xml:space="preserve">Required. Date YYYY-MM-DD, before the cutover date</t>
   </si>
   <si>
-    <t xml:space="preserve">Policies: Sum Insured</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optional. Amount in PHP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Policies: Net Premium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optional. Amount in PHP; the gross premium when empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Policies: Gross Premium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Required. Amount in PHP including taxes, greater than zero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Policies: Commission Rate</t>
+    <t xml:space="preserve">Policies - Motor: Sum Insured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Amount in PHP, at most two decimals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Net Premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Amount in PHP, at most two decimals; the gross premium when empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Gross Premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Amount in PHP including taxes, greater than zero, at most two decimals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Commission Rate</t>
   </si>
   <si>
     <t xml:space="preserve">Optional. Decimal fraction (0.20 for 20%); the insurer default when empty</t>
   </si>
   <si>
-    <t xml:space="preserve">Policies: Billing Mode</t>
+    <t xml:space="preserve">Policies - Motor: Billing Mode</t>
   </si>
   <si>
     <t xml:space="preserve">Optional. broker or direct; the insurer default when empty. Values: Lists sheet, Billing Mode</t>
   </si>
   <si>
-    <t xml:space="preserve">Policies: Payment Status</t>
+    <t xml:space="preserve">Policies - Motor: Payment Status</t>
   </si>
   <si>
     <t xml:space="preserve">Optional. Completed when empty; Pending or Partial when an open item is loaded. Values: Lists sheet, Payment Status</t>
   </si>
   <si>
-    <t xml:space="preserve">Policies: Plate Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optional. Motor only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Policies: Account Executive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optional. Username of the account executive who owns the policy (renewal follow-up)</t>
+    <t xml:space="preserve">Policies - Motor: Account Executive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Username of the Account Executive who owns the policy (renewal follow-up)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Branch code. Values: Lists sheet, Branches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Distribution Channel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Distribution channel code. Values: Lists sheet, Distribution Channels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Business Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. New or Renewal, in the legacy term. Values: Lists sheet, Business Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Previous Legacy Policy Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Policy number of the term before, in the legacy system (reference)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Legacy System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Source of the record; the legacy system of the load when empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Original Currency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Currency of a foreign-currency policy (reference); the amounts above stay in PHP. Values: Lists sheet, Currencies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Original Sum Insured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Sum insured in the original currency (reference)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Exchange Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. PHP per unit of the original currency used by the legacy ledger (reference)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Plate Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Plate, conduction sticker or chassis number required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Conduction Sticker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Chassis Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Engine Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: MV File Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Brand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Values: Lists sheet, Vehicle Brands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Variant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Model Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Four digits, not after the year after the cutover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Body Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Values: Lists sheet, Vehicle Types</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Colour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Seating Capacity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. 1 to 60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Mortgagee / Financier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: TFS Loan Reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Motor: Dealer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Policy Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Client Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Insurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Product code of the Product master (Lists sheet: the products of this sheet). Values: Lists sheet, Products CTPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Insured Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Inception Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Expiry Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Issue Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Sum Insured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Net Premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Gross Premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Commission Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Billing Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Payment Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Account Executive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Distribution Channel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Business Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Previous Legacy Policy Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Legacy System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Original Currency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Original Sum Insured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Exchange Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Plate Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Conduction Sticker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Chassis Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Engine Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: MV File Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: COC Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Certificate of cover number; unique per insurer among in-force CTPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Authentication Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. LTO authentication code of the COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Vehicle Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Values: Lists sheet, CTPL Classes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Brand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - CTPL: Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Policy Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Client Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Insurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Product code of the Product master (Lists sheet: the products of this sheet). Values: Lists sheet, Products Personal Accident</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Insured Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Inception Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Expiry Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Issue Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Sum Insured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Net Premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Gross Premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Commission Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Billing Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Payment Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Account Executive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Distribution Channel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Business Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Previous Legacy Policy Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Legacy System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Original Currency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Original Sum Insured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Exchange Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Values: Lists sheet, Plans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Insured Persons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Group PA: at least 2; PA: 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Beneficiary / Nominee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Personal Accident: Occupation Class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Policy Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Client Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Insurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Product code of the Product master (Lists sheet: the products of this sheet). Values: Lists sheet, Products Credit Life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Insured Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Inception Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Expiry Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Issue Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Sum Insured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Net Premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Gross Premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Commission Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Billing Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Payment Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Account Executive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Distribution Channel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Business Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Previous Legacy Policy Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Legacy System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Original Currency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Original Sum Insured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Exchange Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Borrower Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. The insured name when the Insured Name is empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: TFS Loan Account Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Loan Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Amount in PHP, greater than zero; the sum insured when the Sum Insured is empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Loan Term in Months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. 1 to 120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Loan Release Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Date YYYY-MM-DD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Credit Life: Financier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. TFSPH when empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Policy Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Client Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Insurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Product code of the Product master (Lists sheet: the products of this sheet). Values: Lists sheet, Products Travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Insured Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Inception Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Expiry Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Issue Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Sum Insured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Net Premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Gross Premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Commission Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Billing Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Payment Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Account Executive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Distribution Channel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Business Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Previous Legacy Policy Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Legacy System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Original Currency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Original Sum Insured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Exchange Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Plan / Policy Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. TRV-ST single trip, TRV-ANN annual, TRV-REN renewable. Values: Lists sheet, Travel Plans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Destination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Travel Start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Date YYYY-MM-DD, inside the policy period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Travel End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Date YYYY-MM-DD, inside the policy period; single trip: on or after the cutover date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Travel: Travellers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Other Lines: Policy Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Other Lines: Client Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Other Lines: Insurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Other Lines: Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Product code of the Product master (Lists sheet: the products of this sheet). Values: Lists sheet, Products Other Lines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Other Lines: Insured Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Other Lines: Inception Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Other Lines: Expiry Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Other Lines: Issue Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Other Lines: Sum Insured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Other Lines: Net Premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Other Lines: Gross Premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Other Lines: Commission Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Other Lines: Billing Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Other Lines: Payment Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Other Lines: Account Executive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Other Lines: Branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Other Lines: Distribution Channel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Other Lines: Business Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Other Lines: Previous Legacy Policy Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Other Lines: Legacy System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Other Lines: Original Currency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Other Lines: Original Sum Insured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies - Other Lines: Exchange Rate</t>
   </si>
   <si>
     <t xml:space="preserve">Open Items: Policy Number</t>
@@ -472,6 +1260,63 @@
     <t xml:space="preserve">Required. Amount still unpaid at go-live in PHP, greater than zero</t>
   </si>
   <si>
+    <t xml:space="preserve">Open Items: Currency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. PHP when empty; an open item of another currency is loaded at its peso amount as booked. Values: Lists sheet, Currencies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-Dated Cheques: Drawee Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Bank code of the Bank master, or the bank name. Values: Lists sheet, Banks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-Dated Cheques: Cheque Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-Dated Cheques: Cheque Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Date YYYY-MM-DD, on or after the cutover date (a cheque dated earlier was deposited in the legacy system)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-Dated Cheques: Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Amount in PHP, greater than zero, not more than the open balance of the open item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-Dated Cheques: Policy Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Policy of the open item the cheque pays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-Dated Cheques: Bill Reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Bill Reference of the open item (Open Items sheet or already loaded)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-Dated Cheques: Received Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Date YYYY-MM-DD, before the cutover date; the day before the cutover when empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-Dated Cheques: Storage Location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Vault or safe where the cheque is kept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-Dated Cheques: Drawee Branch</t>
+  </si>
+  <si>
     <t xml:space="preserve">Open Claims: Claim Number</t>
   </si>
   <si>
@@ -481,7 +1326,7 @@
     <t xml:space="preserve">Open Claims: Policy Number</t>
   </si>
   <si>
-    <t xml:space="preserve">Required. Policy of the Policies sheet or already in BrokerVerse</t>
+    <t xml:space="preserve">Required. Policy of the policy sheets or already in BrokerVerse</t>
   </si>
   <si>
     <t xml:space="preserve">Open Claims: Loss Date</t>
@@ -511,7 +1356,7 @@
     <t xml:space="preserve">Open Claims: Outstanding Estimate</t>
   </si>
   <si>
-    <t xml:space="preserve">Required. Amount claimed / reserve still open in PHP</t>
+    <t xml:space="preserve">Required. Amount claimed / reserve still open in PHP, at most two decimals</t>
   </si>
   <si>
     <t xml:space="preserve">Open Claims: Insurer Claim Number</t>
@@ -547,6 +1392,30 @@
     <t xml:space="preserve">Optional. Amount in PHP, no sign; the account balance when it is a credit balance</t>
   </si>
   <si>
+    <t xml:space="preserve">Control Totals: Object</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. One of Clients, Policies, Open Items, Post-Dated Cheques, Open Claims, Opening Balances, Sub-ledger. Values: Lists sheet, Control Objects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control Totals: Measure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. count, gross premium, open balance ... (Instructions: measures per object). Values: Lists sheet, Control Measures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control Totals: Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Product, insurer, ageing bucket, account or bank account; empty for the total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control Totals: Legacy Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Figure of the legacy system at the close of the day before the cutover; amounts in PHP, at most two decimals</t>
+  </si>
+  <si>
     <t xml:space="preserve">Client Type</t>
   </si>
   <si>
@@ -562,7 +1431,61 @@
     <t xml:space="preserve">Insurers</t>
   </si>
   <si>
-    <t xml:space="preserve">Products</t>
+    <t xml:space="preserve">Branches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribution Channels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle Brands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle Types</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTPL Classes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travel Plans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Currencies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control Objects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control Measures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document Types</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Products Motor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Products CTPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Products Personal Accident</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Products Credit Life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Products Travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Products Other Lines</t>
   </si>
   <si>
     <t xml:space="preserve">individual</t>
@@ -577,12 +1500,57 @@
     <t xml:space="preserve">registered</t>
   </si>
   <si>
-    <t xml:space="preserve">APEX</t>
+    <t xml:space="preserve">AXA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Individual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRV-ST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clients</t>
+  </si>
+  <si>
+    <t xml:space="preserve">count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLSCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOTOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPA</t>
   </si>
   <si>
     <t xml:space="preserve">CL-COMP</t>
   </si>
   <si>
+    <t xml:space="preserve">TRAVEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARCEL</t>
+  </si>
+  <si>
     <t xml:space="preserve">corporate</t>
   </si>
   <si>
@@ -595,7 +1563,37 @@
     <t xml:space="preserve">in-review</t>
   </si>
   <si>
-    <t xml:space="preserve">AXA</t>
+    <t xml:space="preserve">FPG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renewal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRV-ANN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JPY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gross premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA</t>
   </si>
   <si>
     <t xml:space="preserve">CL-VOL</t>
@@ -604,72 +1602,195 @@
     <t xml:space="preserve">Partial</t>
   </si>
   <si>
-    <t xml:space="preserve">EVERSAFE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTPL</t>
+    <t xml:space="preserve">MAAGAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hyundai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRV-REN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">net premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OR</t>
   </si>
   <si>
     <t xml:space="preserve">Completed</t>
   </si>
   <si>
-    <t xml:space="preserve">FPG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPA</t>
+    <t xml:space="preserve">MALAYAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isuzu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SGD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-Dated Cheques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sum insured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID</t>
   </si>
   <si>
     <t xml:space="preserve">Refunded</t>
   </si>
   <si>
-    <t xml:space="preserve">GOLDENHORIZON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOTOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INTEGRITY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIBERTYSHIELD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARCEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAAGAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRAVEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MALAYAN</t>
-  </si>
-  <si>
     <t xml:space="preserve">MAPFRE</t>
   </si>
   <si>
+    <t xml:space="preserve">Mitsubishi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Claims</t>
+  </si>
+  <si>
+    <t xml:space="preserve">original amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORCR</t>
+  </si>
+  <si>
     <t xml:space="preserve">MERCANTILE</t>
   </si>
   <si>
+    <t xml:space="preserve">Nissan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opening Balances</t>
+  </si>
+  <si>
+    <t xml:space="preserve">open balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOAN</t>
+  </si>
+  <si>
     <t xml:space="preserve">PIONEER</t>
   </si>
   <si>
-    <t xml:space="preserve">SECUREGUARD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SENTINEL</t>
+    <t xml:space="preserve">Suzuki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EWB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sub-ledger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENDT</t>
   </si>
   <si>
     <t xml:space="preserve">STANDARD</t>
   </si>
   <si>
+    <t xml:space="preserve">Toyota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">outstanding estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAIMFORM</t>
+  </si>
+  <si>
     <t xml:space="preserve">STRONGHOLD</t>
   </si>
   <si>
+    <t xml:space="preserve">MAYBANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">debit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MBT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHOTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PBCOM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTIMATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PNB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">due to insurers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTHER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commission receivable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PVB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unapplied collections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCBC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cash in bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SECB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sap trial balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBP</t>
+  </si>
+  <si>
     <t xml:space="preserve">Client Code *</t>
   </si>
   <si>
@@ -796,10 +1917,73 @@
     <t xml:space="preserve">Commission Rate</t>
   </si>
   <si>
+    <t xml:space="preserve">Account Executive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribution Channel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous Legacy Policy Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Original Currency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Original Sum Insured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exchange Rate</t>
+  </si>
+  <si>
     <t xml:space="preserve">Plate Number</t>
   </si>
   <si>
-    <t xml:space="preserve">Account Executive</t>
+    <t xml:space="preserve">Conduction Sticker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chassis Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engine Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MV File Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Body Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seating Capacity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mortgagee / Financier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TFS Loan Reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dealer</t>
   </si>
   <si>
     <t xml:space="preserve">SAMPLE PC-MLY-2026-000101</t>
@@ -829,6 +2013,156 @@
     <t xml:space="preserve">NCA 4521</t>
   </si>
   <si>
+    <t xml:space="preserve">MHFXX12G0P0012345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOYOTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3 XLE CVT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TFSPH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TFS-LN-0088123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC Number *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Authentication Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMPLE CTPL-MLY-2026-004512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">610.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00451234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AU7781234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private car</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insured Persons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beneficiary / Nominee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupation Class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMPLE PA-MLY-2026-000310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1250.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borrower Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TFS Loan Account Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan Amount *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan Term in Months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan Release Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Financier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMPLE CL-2026-000077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8400.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">980000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan / Policy Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travel Start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travel End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travellers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMPLE TRV-2026-000940</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2500000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1890.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worldwide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMPLE PCL-2026-000015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">250.00</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bill Reference *</t>
   </si>
   <si>
@@ -841,6 +2175,9 @@
     <t xml:space="preserve">Open Balance *</t>
   </si>
   <si>
+    <t xml:space="preserve">Currency</t>
+  </si>
+  <si>
     <t xml:space="preserve">DN-2026-08812</t>
   </si>
   <si>
@@ -850,6 +2187,48 @@
     <t xml:space="preserve">20000</t>
   </si>
   <si>
+    <t xml:space="preserve">Drawee Bank *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheque Number *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheque Date *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Received Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Storage Location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drawee Branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMPLE PNB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0001234567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-11-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10000.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC-MLY-2026-000101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head Office vault</t>
+  </si>
+  <si>
     <t xml:space="preserve">Claim Number *</t>
   </si>
   <si>
@@ -880,9 +2259,6 @@
     <t xml:space="preserve">SAMPLE OLD-CLM-2026-0042</t>
   </si>
   <si>
-    <t xml:space="preserve">PC-MLY-2026-000101</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026-09-12</t>
   </si>
   <si>
@@ -920,6 +2296,57 @@
   </si>
   <si>
     <t xml:space="preserve">1250000.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Object *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measure *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy Value *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMPLE Policies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">migration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Objects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">clients,policies-motor,policies-ctpl,policies-pa,policies-credit-life,policies-travel,policies-other,open-items,post-dated-cheques,claims,opening-balances,control-totals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Layout version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74776e38acadb345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated at</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-10T07:27:21.818Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated by</t>
   </si>
 </sst>
 </file>
@@ -927,7 +2354,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -1107,7 +2534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B311"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -1199,26 +2626,26 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="10"/>
+      <c r="B12" s="4" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="4" t="s">
+      <c r="A14" s="10" t="s">
         <v>24</v>
       </c>
+      <c r="B14" s="10"/>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
@@ -1241,326 +2668,326 @@
         <v>29</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="10"/>
+      <c r="B18" s="4" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="10"/>
+      <c r="A23" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>47</v>
-      </c>
+      <c r="B27" s="10"/>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="B29" s="10"/>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>58</v>
-      </c>
+      <c r="B33" s="10"/>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B37" s="10"/>
+      <c r="A37" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>69</v>
-      </c>
+      <c r="A39" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B39" s="10"/>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B45" s="10"/>
+      <c r="A45" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>86</v>
-      </c>
+      <c r="A49" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B49" s="10"/>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="B56" s="4" t="s">
         <v>98</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B57" s="4" t="s">
-        <v>91</v>
-      </c>
     </row>
     <row r="58">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B58" s="4" t="s">
-        <v>91</v>
-      </c>
+      <c r="B58" s="10"/>
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
@@ -1591,32 +3018,30 @@
         <v>108</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="B65" s="4" t="s">
+      <c r="A65" s="10" t="s">
         <v>114</v>
       </c>
+      <c r="B65" s="10"/>
     </row>
     <row r="66">
       <c r="A66" s="0" t="s">
@@ -1675,213 +3100,2320 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="0" t="s">
+      <c r="A73" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="B73" s="4" t="s">
-        <v>130</v>
-      </c>
+      <c r="B73" s="10"/>
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="B74" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="B75" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="B76" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="B77" s="4" t="s">
         <v>137</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="B78" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="B79" s="4" t="s">
         <v>141</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="B80" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="B81" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="B82" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B82" s="4" t="s">
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="0" t="s">
-        <v>149</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>150</v>
-      </c>
+      <c r="B83" s="10"/>
     </row>
     <row r="84">
       <c r="A84" s="0" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>91</v>
+        <v>159</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>91</v>
+        <v>164</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="s">
         <v>174</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="B99" s="4" t="s">
         <v>175</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="0" t="s">
+        <v>179</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="0" t="s">
+        <v>181</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="0" t="s">
+        <v>199</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="0" t="s">
+        <v>205</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="0" t="s">
+        <v>219</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="0" t="s">
+        <v>223</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="0" t="s">
+        <v>228</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="0" t="s">
+        <v>229</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="0" t="s">
+        <v>231</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="0" t="s">
+        <v>232</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="0" t="s">
+        <v>233</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="0" t="s">
+        <v>235</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="0" t="s">
+        <v>250</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="0" t="s">
+        <v>251</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="0" t="s">
+        <v>253</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="0" t="s">
+        <v>257</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="0" t="s">
+        <v>262</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="0" t="s">
+        <v>263</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="0" t="s">
+        <v>274</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="0" t="s">
+        <v>276</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="0" t="s">
+        <v>279</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="0" t="s">
+        <v>281</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="0" t="s">
+        <v>283</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="0" t="s">
+        <v>287</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="0" t="s">
+        <v>290</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="0" t="s">
+        <v>291</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="0" t="s">
+        <v>292</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="0" t="s">
+        <v>293</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="0" t="s">
+        <v>295</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="0" t="s">
+        <v>296</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="0" t="s">
+        <v>298</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="0" t="s">
+        <v>299</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="0" t="s">
+        <v>301</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="0" t="s">
+        <v>302</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="0" t="s">
+        <v>303</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="0" t="s">
+        <v>304</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="0" t="s">
+        <v>306</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="0" t="s">
+        <v>308</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="0" t="s">
+        <v>309</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="0" t="s">
+        <v>310</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="0" t="s">
+        <v>311</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="0" t="s">
+        <v>312</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="0" t="s">
+        <v>313</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="0" t="s">
+        <v>317</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="0" t="s">
+        <v>319</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="0" t="s">
+        <v>320</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="0" t="s">
+        <v>321</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="0" t="s">
+        <v>322</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="0" t="s">
+        <v>323</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="0" t="s">
+        <v>324</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="0" t="s">
+        <v>325</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="0" t="s">
+        <v>326</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="0" t="s">
+        <v>327</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="0" t="s">
+        <v>328</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="0" t="s">
+        <v>329</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="0" t="s">
+        <v>330</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="0" t="s">
+        <v>331</v>
+      </c>
+      <c r="B219" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="0" t="s">
+        <v>332</v>
+      </c>
+      <c r="B220" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="0" t="s">
+        <v>333</v>
+      </c>
+      <c r="B221" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="0" t="s">
+        <v>334</v>
+      </c>
+      <c r="B222" s="4" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="0" t="s">
+        <v>336</v>
+      </c>
+      <c r="B223" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="0" t="s">
+        <v>337</v>
+      </c>
+      <c r="B224" s="4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="0" t="s">
+        <v>339</v>
+      </c>
+      <c r="B225" s="4" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="0" t="s">
+        <v>341</v>
+      </c>
+      <c r="B226" s="4" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="0" t="s">
+        <v>343</v>
+      </c>
+      <c r="B227" s="4" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="0" t="s">
+        <v>345</v>
+      </c>
+      <c r="B228" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="0" t="s">
+        <v>346</v>
+      </c>
+      <c r="B229" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="0" t="s">
+        <v>347</v>
+      </c>
+      <c r="B230" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="0" t="s">
+        <v>348</v>
+      </c>
+      <c r="B231" s="4" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="0" t="s">
+        <v>350</v>
+      </c>
+      <c r="B232" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="0" t="s">
+        <v>351</v>
+      </c>
+      <c r="B233" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="0" t="s">
+        <v>352</v>
+      </c>
+      <c r="B234" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="0" t="s">
+        <v>353</v>
+      </c>
+      <c r="B235" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="0" t="s">
+        <v>354</v>
+      </c>
+      <c r="B236" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="0" t="s">
+        <v>355</v>
+      </c>
+      <c r="B237" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="B238" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="0" t="s">
+        <v>357</v>
+      </c>
+      <c r="B239" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="0" t="s">
+        <v>358</v>
+      </c>
+      <c r="B240" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="0" t="s">
+        <v>359</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="0" t="s">
+        <v>360</v>
+      </c>
+      <c r="B242" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="0" t="s">
+        <v>361</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="0" t="s">
+        <v>362</v>
+      </c>
+      <c r="B244" s="4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="0" t="s">
+        <v>363</v>
+      </c>
+      <c r="B245" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="0" t="s">
+        <v>364</v>
+      </c>
+      <c r="B246" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="0" t="s">
+        <v>365</v>
+      </c>
+      <c r="B247" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="0" t="s">
+        <v>366</v>
+      </c>
+      <c r="B248" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="0" t="s">
+        <v>367</v>
+      </c>
+      <c r="B249" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="0" t="s">
+        <v>368</v>
+      </c>
+      <c r="B250" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="0" t="s">
+        <v>369</v>
+      </c>
+      <c r="B251" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="0" t="s">
+        <v>371</v>
+      </c>
+      <c r="B252" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="0" t="s">
+        <v>372</v>
+      </c>
+      <c r="B253" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="0" t="s">
+        <v>374</v>
+      </c>
+      <c r="B254" s="4" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="0" t="s">
+        <v>376</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="B256" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="B257" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="0" t="s">
+        <v>379</v>
+      </c>
+      <c r="B258" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="0" t="s">
+        <v>380</v>
+      </c>
+      <c r="B259" s="4" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="0" t="s">
+        <v>382</v>
+      </c>
+      <c r="B260" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="0" t="s">
+        <v>383</v>
+      </c>
+      <c r="B261" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="0" t="s">
+        <v>384</v>
+      </c>
+      <c r="B262" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="0" t="s">
+        <v>385</v>
+      </c>
+      <c r="B263" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="0" t="s">
+        <v>386</v>
+      </c>
+      <c r="B264" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="0" t="s">
+        <v>387</v>
+      </c>
+      <c r="B265" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="0" t="s">
+        <v>388</v>
+      </c>
+      <c r="B266" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="0" t="s">
+        <v>389</v>
+      </c>
+      <c r="B267" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="0" t="s">
+        <v>390</v>
+      </c>
+      <c r="B268" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="0" t="s">
+        <v>391</v>
+      </c>
+      <c r="B269" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="0" t="s">
+        <v>392</v>
+      </c>
+      <c r="B270" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="0" t="s">
+        <v>393</v>
+      </c>
+      <c r="B271" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="0" t="s">
+        <v>394</v>
+      </c>
+      <c r="B272" s="4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="0" t="s">
+        <v>395</v>
+      </c>
+      <c r="B273" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="0" t="s">
+        <v>396</v>
+      </c>
+      <c r="B274" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="0" t="s">
+        <v>397</v>
+      </c>
+      <c r="B275" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="0" t="s">
+        <v>398</v>
+      </c>
+      <c r="B276" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="0" t="s">
+        <v>399</v>
+      </c>
+      <c r="B277" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="0" t="s">
+        <v>400</v>
+      </c>
+      <c r="B278" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="0" t="s">
+        <v>401</v>
+      </c>
+      <c r="B279" s="4" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="0" t="s">
+        <v>403</v>
+      </c>
+      <c r="B280" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="0" t="s">
+        <v>405</v>
+      </c>
+      <c r="B281" s="4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="0" t="s">
+        <v>407</v>
+      </c>
+      <c r="B282" s="4" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="0" t="s">
+        <v>409</v>
+      </c>
+      <c r="B283" s="4" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="0" t="s">
+        <v>411</v>
+      </c>
+      <c r="B284" s="4" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="0" t="s">
+        <v>413</v>
+      </c>
+      <c r="B285" s="4" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="0" t="s">
+        <v>415</v>
+      </c>
+      <c r="B286" s="4" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="0" t="s">
+        <v>417</v>
+      </c>
+      <c r="B287" s="4" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="B288" s="4" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="0" t="s">
+        <v>421</v>
+      </c>
+      <c r="B289" s="4" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="0" t="s">
+        <v>423</v>
+      </c>
+      <c r="B290" s="4" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="0" t="s">
+        <v>425</v>
+      </c>
+      <c r="B291" s="4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="0" t="s">
+        <v>427</v>
+      </c>
+      <c r="B292" s="4" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="0" t="s">
+        <v>429</v>
+      </c>
+      <c r="B293" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="0" t="s">
+        <v>430</v>
+      </c>
+      <c r="B294" s="4" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="0" t="s">
+        <v>432</v>
+      </c>
+      <c r="B295" s="4" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="0" t="s">
+        <v>434</v>
+      </c>
+      <c r="B296" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="B297" s="4" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="0" t="s">
+        <v>437</v>
+      </c>
+      <c r="B298" s="4" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="B299" s="4" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="0" t="s">
+        <v>441</v>
+      </c>
+      <c r="B300" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="0" t="s">
+        <v>442</v>
+      </c>
+      <c r="B301" s="4" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="B302" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="0" t="s">
+        <v>445</v>
+      </c>
+      <c r="B303" s="4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="0" t="s">
+        <v>447</v>
+      </c>
+      <c r="B304" s="4" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="0" t="s">
+        <v>449</v>
+      </c>
+      <c r="B305" s="4" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="0" t="s">
+        <v>451</v>
+      </c>
+      <c r="B306" s="4" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="0" t="s">
+        <v>453</v>
+      </c>
+      <c r="B307" s="4" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="B308" s="4" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="0" t="s">
+        <v>457</v>
+      </c>
+      <c r="B309" s="4" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="0" t="s">
+        <v>459</v>
+      </c>
+      <c r="B310" s="4" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="0" t="s">
+        <v>461</v>
+      </c>
+      <c r="B311" s="4" t="s">
+        <v>462</v>
+      </c>
+    </row>
   </sheetData>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19" style="11" customWidth="1"/>
+    <col min="2" max="2" width="20" style="11" customWidth="1"/>
+    <col min="3" max="3" width="14" style="11" customWidth="1"/>
+    <col min="4" max="4" width="21" style="11" customWidth="1"/>
+    <col min="5" max="5" width="18" style="11" customWidth="1"/>
+    <col min="6" max="6" width="14" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>712</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>715</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>717</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>718</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>719</v>
+      </c>
+      <c r="F2" s="9"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="F2:F5000">
+      <formula1>Lists!$N$2:$N$6</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17" style="11" customWidth="1"/>
+    <col min="2" max="2" width="19" style="11" customWidth="1"/>
+    <col min="3" max="3" width="17" style="11" customWidth="1"/>
+    <col min="4" max="4" width="14" style="11" customWidth="1"/>
+    <col min="5" max="5" width="19" style="11" customWidth="1"/>
+    <col min="6" max="6" width="20" style="11" customWidth="1"/>
+    <col min="7" max="7" width="19" style="11" customWidth="1"/>
+    <col min="8" max="8" width="22" style="11" customWidth="1"/>
+    <col min="9" max="9" width="19" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>712</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>724</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>725</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>727</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>728</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>730</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>731</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>717</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>732</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="I2" s="9"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="A2:A5000">
+      <formula1>Lists!$O$2:$O$18</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18" style="11" customWidth="1"/>
+    <col min="2" max="2" width="19" style="11" customWidth="1"/>
+    <col min="3" max="3" width="15" style="11" customWidth="1"/>
+    <col min="4" max="4" width="19" style="11" customWidth="1"/>
+    <col min="5" max="5" width="14" style="11" customWidth="1"/>
+    <col min="6" max="6" width="15" style="11" customWidth="1"/>
+    <col min="7" max="7" width="17" style="11" customWidth="1"/>
+    <col min="8" max="8" width="26" style="11" customWidth="1"/>
+    <col min="9" max="9" width="26" style="11" customWidth="1"/>
+    <col min="10" max="10" width="14" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>737</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>739</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>740</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>743</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>731</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>745</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>746</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>747</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>748</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>749</v>
+      </c>
+      <c r="J2" s="9"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="E2:E5000">
+      <formula1>Lists!$D$2:$D$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18" style="11" customWidth="1"/>
+    <col min="2" max="2" width="18" style="11" customWidth="1"/>
+    <col min="3" max="3" width="14" style="11" customWidth="1"/>
+    <col min="4" max="4" width="14" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>750</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>751</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>752</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>754</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>755</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>756</v>
+      </c>
+      <c r="D2" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14" style="11" customWidth="1"/>
+    <col min="2" max="2" width="14" style="11" customWidth="1"/>
+    <col min="3" max="3" width="14" style="11" customWidth="1"/>
+    <col min="4" max="4" width="18" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>757</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>759</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>761</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>756</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="A2:A5000">
+      <formula1>Lists!$P$2:$P$8</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="B2:B5000">
+      <formula1>Lists!$Q$2:$Q$17</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>763</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>765</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>767</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>771</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>773</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatCells="0" formatColumns="0"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" style="11" customWidth="1"/>
@@ -1890,109 +5422,353 @@
     <col min="4" max="4" width="16" style="11" customWidth="1"/>
     <col min="5" max="5" width="14" style="11" customWidth="1"/>
     <col min="6" max="6" width="14" style="11" customWidth="1"/>
+    <col min="7" max="7" width="25" style="11" customWidth="1"/>
+    <col min="8" max="8" width="17" style="11" customWidth="1"/>
+    <col min="9" max="9" width="18" style="11" customWidth="1"/>
+    <col min="10" max="10" width="17" style="11" customWidth="1"/>
+    <col min="11" max="11" width="16" style="11" customWidth="1"/>
+    <col min="12" max="12" width="14" style="11" customWidth="1"/>
+    <col min="13" max="13" width="16" style="11" customWidth="1"/>
+    <col min="14" max="14" width="14" style="11" customWidth="1"/>
+    <col min="15" max="15" width="14" style="11" customWidth="1"/>
+    <col min="16" max="16" width="19" style="11" customWidth="1"/>
+    <col min="17" max="17" width="20" style="11" customWidth="1"/>
+    <col min="18" max="18" width="18" style="11" customWidth="1"/>
+    <col min="19" max="19" width="18" style="11" customWidth="1"/>
+    <col min="20" max="20" width="17" style="11" customWidth="1"/>
+    <col min="21" max="21" width="30" style="11" customWidth="1"/>
+    <col min="22" max="22" width="24" style="11" customWidth="1"/>
+    <col min="23" max="23" width="19" style="11" customWidth="1"/>
+    <col min="24" max="24" width="24" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="20" customHeight="1">
+    <row r="1" spans="1:24" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>176</v>
+        <v>463</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>177</v>
+        <v>464</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>178</v>
+        <v>465</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>179</v>
+        <v>466</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>180</v>
+        <v>467</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>181</v>
+        <v>468</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>478</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="S1" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="V1" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="W1" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="X1" s="8" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="s">
-        <v>182</v>
+        <v>487</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>183</v>
+        <v>488</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>184</v>
+        <v>489</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>185</v>
+        <v>490</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>186</v>
+        <v>491</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>187</v>
+        <v>492</v>
+      </c>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11" t="s">
+        <v>493</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>494</v>
+      </c>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11" t="s">
+        <v>495</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>496</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>497</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>499</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>500</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>501</v>
+      </c>
+      <c r="S2" s="11" t="s">
+        <v>502</v>
+      </c>
+      <c r="T2" s="11" t="s">
+        <v>503</v>
+      </c>
+      <c r="U2" s="11" t="s">
+        <v>504</v>
+      </c>
+      <c r="V2" s="11" t="s">
+        <v>505</v>
+      </c>
+      <c r="W2" s="11" t="s">
+        <v>506</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
-        <v>188</v>
+        <v>508</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>189</v>
+        <v>509</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>190</v>
+        <v>510</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>191</v>
+        <v>511</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>193</v>
-      </c>
+        <v>512</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11" t="s">
+        <v>515</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>516</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>517</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>518</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>519</v>
+      </c>
+      <c r="Q3" s="11" t="s">
+        <v>520</v>
+      </c>
+      <c r="R3" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="S3" s="11"/>
+      <c r="T3" s="11"/>
+      <c r="U3" s="11" t="s">
+        <v>522</v>
+      </c>
+      <c r="V3" s="11" t="s">
+        <v>523</v>
+      </c>
+      <c r="W3" s="11"/>
+      <c r="X3" s="11"/>
     </row>
     <row r="4">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11" t="s">
-        <v>194</v>
+        <v>524</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>196</v>
-      </c>
+        <v>525</v>
+      </c>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11" t="s">
+        <v>526</v>
+      </c>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11" t="s">
+        <v>527</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>528</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>529</v>
+      </c>
+      <c r="P4" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="Q4" s="11" t="s">
+        <v>531</v>
+      </c>
+      <c r="R4" s="11" t="s">
+        <v>532</v>
+      </c>
+      <c r="S4" s="11"/>
+      <c r="T4" s="11"/>
+      <c r="U4" s="11"/>
+      <c r="V4" s="11"/>
+      <c r="W4" s="11"/>
+      <c r="X4" s="11"/>
     </row>
     <row r="5">
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
       <c r="C5" s="11" t="s">
-        <v>197</v>
+        <v>533</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>199</v>
-      </c>
+        <v>534</v>
+      </c>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11" t="s">
+        <v>535</v>
+      </c>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11" t="s">
+        <v>536</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>537</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>538</v>
+      </c>
+      <c r="Q5" s="11" t="s">
+        <v>539</v>
+      </c>
+      <c r="R5" s="11" t="s">
+        <v>540</v>
+      </c>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
     </row>
     <row r="6">
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11" t="s">
-        <v>200</v>
+        <v>541</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>202</v>
-      </c>
+        <v>542</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11" t="s">
+        <v>543</v>
+      </c>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11" t="s">
+        <v>544</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>545</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>546</v>
+      </c>
+      <c r="Q6" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="R6" s="11" t="s">
+        <v>548</v>
+      </c>
+      <c r="S6" s="11"/>
+      <c r="T6" s="11"/>
+      <c r="U6" s="11"/>
+      <c r="V6" s="11"/>
+      <c r="W6" s="11"/>
+      <c r="X6" s="11"/>
     </row>
     <row r="7">
       <c r="A7" s="11"/>
@@ -2000,11 +5776,37 @@
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
       <c r="E7" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>204</v>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11" t="s">
+        <v>550</v>
+      </c>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11" t="s">
+        <v>551</v>
+      </c>
+      <c r="P7" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="Q7" s="11" t="s">
+        <v>553</v>
+      </c>
+      <c r="R7" s="11" t="s">
+        <v>554</v>
+      </c>
+      <c r="S7" s="11"/>
+      <c r="T7" s="11"/>
+      <c r="U7" s="11"/>
+      <c r="V7" s="11"/>
+      <c r="W7" s="11"/>
+      <c r="X7" s="11"/>
     </row>
     <row r="8">
       <c r="A8" s="11"/>
@@ -2012,11 +5814,37 @@
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
       <c r="E8" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>206</v>
-      </c>
+        <v>555</v>
+      </c>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11" t="s">
+        <v>556</v>
+      </c>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11" t="s">
+        <v>557</v>
+      </c>
+      <c r="P8" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="Q8" s="11" t="s">
+        <v>559</v>
+      </c>
+      <c r="R8" s="11" t="s">
+        <v>560</v>
+      </c>
+      <c r="S8" s="11"/>
+      <c r="T8" s="11"/>
+      <c r="U8" s="11"/>
+      <c r="V8" s="11"/>
+      <c r="W8" s="11"/>
+      <c r="X8" s="11"/>
     </row>
     <row r="9">
       <c r="A9" s="11"/>
@@ -2024,11 +5852,35 @@
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>208</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11" t="s">
+        <v>562</v>
+      </c>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11" t="s">
+        <v>564</v>
+      </c>
+      <c r="R9" s="11" t="s">
+        <v>565</v>
+      </c>
+      <c r="S9" s="11"/>
+      <c r="T9" s="11"/>
+      <c r="U9" s="11"/>
+      <c r="V9" s="11"/>
+      <c r="W9" s="11"/>
+      <c r="X9" s="11"/>
     </row>
     <row r="10">
       <c r="A10" s="11"/>
@@ -2036,79 +5888,277 @@
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11" t="s">
-        <v>209</v>
+        <v>566</v>
       </c>
       <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11" t="s">
+        <v>567</v>
+      </c>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="R10" s="11" t="s">
+        <v>569</v>
+      </c>
+      <c r="S10" s="11"/>
+      <c r="T10" s="11"/>
+      <c r="U10" s="11"/>
+      <c r="V10" s="11"/>
+      <c r="W10" s="11"/>
+      <c r="X10" s="11"/>
     </row>
     <row r="11">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
-      <c r="E11" s="11" t="s">
-        <v>210</v>
-      </c>
+      <c r="E11" s="11"/>
       <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11" t="s">
+        <v>570</v>
+      </c>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11" t="s">
+        <v>571</v>
+      </c>
+      <c r="R11" s="11" t="s">
+        <v>572</v>
+      </c>
+      <c r="S11" s="11"/>
+      <c r="T11" s="11"/>
+      <c r="U11" s="11"/>
+      <c r="V11" s="11"/>
+      <c r="W11" s="11"/>
+      <c r="X11" s="11"/>
     </row>
     <row r="12">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
-      <c r="E12" s="11" t="s">
-        <v>211</v>
-      </c>
+      <c r="E12" s="11"/>
       <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11" t="s">
+        <v>573</v>
+      </c>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11" t="s">
+        <v>574</v>
+      </c>
+      <c r="R12" s="11" t="s">
+        <v>575</v>
+      </c>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
+      <c r="V12" s="11"/>
+      <c r="W12" s="11"/>
+      <c r="X12" s="11"/>
     </row>
     <row r="13">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
-      <c r="E13" s="11" t="s">
-        <v>212</v>
-      </c>
+      <c r="E13" s="11"/>
       <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11" t="s">
+        <v>576</v>
+      </c>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11" t="s">
+        <v>577</v>
+      </c>
+      <c r="R13" s="11" t="s">
+        <v>578</v>
+      </c>
+      <c r="S13" s="11"/>
+      <c r="T13" s="11"/>
+      <c r="U13" s="11"/>
+      <c r="V13" s="11"/>
+      <c r="W13" s="11"/>
+      <c r="X13" s="11"/>
     </row>
     <row r="14">
       <c r="A14" s="11"/>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
-      <c r="E14" s="11" t="s">
-        <v>213</v>
-      </c>
+      <c r="E14" s="11"/>
       <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11" t="s">
+        <v>579</v>
+      </c>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11" t="s">
+        <v>580</v>
+      </c>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="11"/>
+      <c r="V14" s="11"/>
+      <c r="W14" s="11"/>
+      <c r="X14" s="11"/>
     </row>
     <row r="15">
       <c r="A15" s="11"/>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
-      <c r="E15" s="11" t="s">
-        <v>214</v>
-      </c>
+      <c r="E15" s="11"/>
       <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="11"/>
+      <c r="W15" s="11"/>
+      <c r="X15" s="11"/>
     </row>
     <row r="16">
       <c r="A16" s="11"/>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
-      <c r="E16" s="11" t="s">
-        <v>215</v>
-      </c>
+      <c r="E16" s="11"/>
       <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11" t="s">
+        <v>583</v>
+      </c>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11" t="s">
+        <v>584</v>
+      </c>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="11"/>
+      <c r="W16" s="11"/>
+      <c r="X16" s="11"/>
     </row>
     <row r="17">
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
-      <c r="E17" s="11" t="s">
-        <v>216</v>
-      </c>
+      <c r="E17" s="11"/>
       <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11" t="s">
+        <v>585</v>
+      </c>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11" t="s">
+        <v>586</v>
+      </c>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
+      <c r="V17" s="11"/>
+      <c r="W17" s="11"/>
+      <c r="X17" s="11"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11" t="s">
+        <v>587</v>
+      </c>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="11"/>
+      <c r="T18" s="11"/>
+      <c r="U18" s="11"/>
+      <c r="V18" s="11"/>
+      <c r="W18" s="11"/>
+      <c r="X18" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2141,104 +6191,104 @@
   <sheetData>
     <row r="1" spans="1:17" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>217</v>
+        <v>588</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>218</v>
+        <v>589</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>219</v>
+        <v>590</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>220</v>
+        <v>591</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>221</v>
+        <v>592</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>222</v>
+        <v>593</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>223</v>
+        <v>594</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>224</v>
+        <v>595</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>225</v>
+        <v>596</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>226</v>
+        <v>597</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>227</v>
+        <v>598</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>228</v>
+        <v>599</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>229</v>
+        <v>600</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>230</v>
+        <v>601</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>231</v>
+        <v>602</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>232</v>
+        <v>603</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>233</v>
+        <v>604</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>234</v>
+        <v>605</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>182</v>
+        <v>487</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>235</v>
+        <v>606</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>236</v>
+        <v>607</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>237</v>
+        <v>608</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>238</v>
+        <v>609</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>239</v>
+        <v>610</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>240</v>
+        <v>611</v>
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="9" t="s">
-        <v>241</v>
+        <v>612</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>242</v>
+        <v>613</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>243</v>
+        <v>614</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>244</v>
+        <v>615</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>245</v>
+        <v>616</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>246</v>
+        <v>617</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>247</v>
+        <v>618</v>
       </c>
     </row>
   </sheetData>
@@ -2253,7 +6303,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:AL2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19" style="11" customWidth="1"/>
@@ -2270,117 +6320,265 @@
     <col min="12" max="12" width="21" style="11" customWidth="1"/>
     <col min="13" max="13" width="18" style="11" customWidth="1"/>
     <col min="14" max="14" width="20" style="11" customWidth="1"/>
-    <col min="15" max="15" width="18" style="11" customWidth="1"/>
-    <col min="16" max="16" width="23" style="11" customWidth="1"/>
+    <col min="15" max="15" width="23" style="11" customWidth="1"/>
+    <col min="16" max="16" width="14" style="11" customWidth="1"/>
+    <col min="17" max="17" width="26" style="11" customWidth="1"/>
+    <col min="18" max="18" width="19" style="11" customWidth="1"/>
+    <col min="19" max="19" width="35" style="11" customWidth="1"/>
+    <col min="20" max="20" width="19" style="11" customWidth="1"/>
+    <col min="21" max="21" width="23" style="11" customWidth="1"/>
+    <col min="22" max="22" width="26" style="11" customWidth="1"/>
+    <col min="23" max="23" width="19" style="11" customWidth="1"/>
+    <col min="24" max="24" width="18" style="11" customWidth="1"/>
+    <col min="25" max="25" width="24" style="11" customWidth="1"/>
+    <col min="26" max="26" width="20" style="11" customWidth="1"/>
+    <col min="27" max="27" width="19" style="11" customWidth="1"/>
+    <col min="28" max="28" width="20" style="11" customWidth="1"/>
+    <col min="29" max="29" width="14" style="11" customWidth="1"/>
+    <col min="30" max="30" width="14" style="11" customWidth="1"/>
+    <col min="31" max="31" width="14" style="11" customWidth="1"/>
+    <col min="32" max="32" width="16" style="11" customWidth="1"/>
+    <col min="33" max="33" width="15" style="11" customWidth="1"/>
+    <col min="34" max="34" width="14" style="11" customWidth="1"/>
+    <col min="35" max="35" width="22" style="11" customWidth="1"/>
+    <col min="36" max="36" width="27" style="11" customWidth="1"/>
+    <col min="37" max="37" width="24" style="11" customWidth="1"/>
+    <col min="38" max="38" width="14" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="20" customHeight="1">
+    <row r="1" spans="1:38" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>248</v>
+        <v>619</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>217</v>
+        <v>588</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>249</v>
+        <v>620</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>250</v>
+        <v>621</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>251</v>
+        <v>622</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>252</v>
+        <v>623</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>253</v>
+        <v>624</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>254</v>
+        <v>625</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>255</v>
+        <v>626</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>256</v>
+        <v>627</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>257</v>
+        <v>628</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>258</v>
+        <v>629</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>177</v>
+        <v>464</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>178</v>
+        <v>465</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>259</v>
+        <v>630</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>260</v>
+        <v>631</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="S1" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="V1" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="W1" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="X1" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="Y1" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="Z1" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="AA1" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="AB1" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="AC1" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="AD1" s="8" t="s">
+        <v>644</v>
+      </c>
+      <c r="AE1" s="8" t="s">
+        <v>645</v>
+      </c>
+      <c r="AF1" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="AG1" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="AH1" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="AI1" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="AJ1" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="AK1" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="AL1" s="8" t="s">
+        <v>652</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>261</v>
+        <v>653</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>262</v>
+        <v>654</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>209</v>
+        <v>534</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>202</v>
+        <v>502</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>263</v>
+        <v>655</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>264</v>
+        <v>656</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>265</v>
+        <v>657</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>266</v>
+        <v>658</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>267</v>
+        <v>659</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>268</v>
+        <v>660</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>183</v>
+        <v>488</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="O2" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="P2" s="9"/>
+        <v>533</v>
+      </c>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9" t="s">
+        <v>663</v>
+      </c>
+      <c r="AD2" s="9" t="s">
+        <v>664</v>
+      </c>
+      <c r="AE2" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="AF2" s="9" t="s">
+        <v>666</v>
+      </c>
+      <c r="AG2" s="9"/>
+      <c r="AH2" s="9"/>
+      <c r="AI2" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="AJ2" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="AK2" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="AL2" s="9"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="10">
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="C2:C5000">
-      <formula1>Lists!$E$2:$E$17</formula1>
+      <formula1>Lists!$E$2:$E$10</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="D2:D5000">
-      <formula1>Lists!$F$2:$F$9</formula1>
+      <formula1>Lists!$S$2:$S$2</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="M2:M5000">
       <formula1>Lists!$B$2:$B$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="N2:N5000">
       <formula1>Lists!$C$2:$C$6</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="P2:P5000">
+      <formula1>Lists!$F$2:$F$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="Q2:Q5000">
+      <formula1>Lists!$G$2:$G$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="R2:R5000">
+      <formula1>Lists!$H$2:$H$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="U2:U5000">
+      <formula1>Lists!$N$2:$N$6</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="AC2:AC5000">
+      <formula1>Lists!$I$2:$I$9</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="AG2:AG5000">
+      <formula1>Lists!$J$2:$J$2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2389,138 +6587,457 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19" style="11" customWidth="1"/>
-    <col min="2" max="2" width="20" style="11" customWidth="1"/>
+    <col min="2" max="2" width="17" style="11" customWidth="1"/>
     <col min="3" max="3" width="14" style="11" customWidth="1"/>
-    <col min="4" max="4" width="21" style="11" customWidth="1"/>
+    <col min="4" max="4" width="14" style="11" customWidth="1"/>
     <col min="5" max="5" width="18" style="11" customWidth="1"/>
+    <col min="6" max="6" width="20" style="11" customWidth="1"/>
+    <col min="7" max="7" width="17" style="11" customWidth="1"/>
+    <col min="8" max="8" width="16" style="11" customWidth="1"/>
+    <col min="9" max="9" width="17" style="11" customWidth="1"/>
+    <col min="10" max="10" width="17" style="11" customWidth="1"/>
+    <col min="11" max="11" width="19" style="11" customWidth="1"/>
+    <col min="12" max="12" width="21" style="11" customWidth="1"/>
+    <col min="13" max="13" width="18" style="11" customWidth="1"/>
+    <col min="14" max="14" width="20" style="11" customWidth="1"/>
+    <col min="15" max="15" width="23" style="11" customWidth="1"/>
+    <col min="16" max="16" width="14" style="11" customWidth="1"/>
+    <col min="17" max="17" width="26" style="11" customWidth="1"/>
+    <col min="18" max="18" width="19" style="11" customWidth="1"/>
+    <col min="19" max="19" width="35" style="11" customWidth="1"/>
+    <col min="20" max="20" width="19" style="11" customWidth="1"/>
+    <col min="21" max="21" width="23" style="11" customWidth="1"/>
+    <col min="22" max="22" width="26" style="11" customWidth="1"/>
+    <col min="23" max="23" width="19" style="11" customWidth="1"/>
+    <col min="24" max="24" width="18" style="11" customWidth="1"/>
+    <col min="25" max="25" width="24" style="11" customWidth="1"/>
+    <col min="26" max="26" width="20" style="11" customWidth="1"/>
+    <col min="27" max="27" width="19" style="11" customWidth="1"/>
+    <col min="28" max="28" width="20" style="11" customWidth="1"/>
+    <col min="29" max="29" width="16" style="11" customWidth="1"/>
+    <col min="30" max="30" width="25" style="11" customWidth="1"/>
+    <col min="31" max="31" width="18" style="11" customWidth="1"/>
+    <col min="32" max="32" width="14" style="11" customWidth="1"/>
+    <col min="33" max="33" width="14" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="20" customHeight="1">
+    <row r="1" spans="1:33" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>248</v>
+        <v>619</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>270</v>
+        <v>588</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>271</v>
+        <v>620</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>272</v>
+        <v>621</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>273</v>
+        <v>622</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="S1" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="V1" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="W1" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="X1" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="Y1" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="Z1" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="AA1" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="AB1" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="AC1" s="8" t="s">
+        <v>670</v>
+      </c>
+      <c r="AD1" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="AE1" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="AF1" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="AG1" s="8" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>261</v>
+        <v>673</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>274</v>
+        <v>654</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>275</v>
+        <v>534</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>276</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>656</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>657</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9" t="s">
+        <v>676</v>
+      </c>
+      <c r="AD2" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="AE2" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="AF2" s="9"/>
+      <c r="AG2" s="9"/>
     </row>
   </sheetData>
+  <dataValidations count="10">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="C2:C5000">
+      <formula1>Lists!$E$2:$E$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="D2:D5000">
+      <formula1>Lists!$T$2:$T$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="M2:M5000">
+      <formula1>Lists!$B$2:$B$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="N2:N5000">
+      <formula1>Lists!$C$2:$C$6</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="P2:P5000">
+      <formula1>Lists!$F$2:$F$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="Q2:Q5000">
+      <formula1>Lists!$G$2:$G$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="R2:R5000">
+      <formula1>Lists!$H$2:$H$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="U2:U5000">
+      <formula1>Lists!$N$2:$N$6</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="AE2:AE5000">
+      <formula1>Lists!$K$2:$K$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="AF2:AF5000">
+      <formula1>Lists!$I$2:$I$9</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18" style="11" customWidth="1"/>
-    <col min="2" max="2" width="19" style="11" customWidth="1"/>
-    <col min="3" max="3" width="15" style="11" customWidth="1"/>
-    <col min="4" max="4" width="19" style="11" customWidth="1"/>
-    <col min="5" max="5" width="14" style="11" customWidth="1"/>
-    <col min="6" max="6" width="15" style="11" customWidth="1"/>
+    <col min="1" max="1" width="19" style="11" customWidth="1"/>
+    <col min="2" max="2" width="17" style="11" customWidth="1"/>
+    <col min="3" max="3" width="14" style="11" customWidth="1"/>
+    <col min="4" max="4" width="14" style="11" customWidth="1"/>
+    <col min="5" max="5" width="18" style="11" customWidth="1"/>
+    <col min="6" max="6" width="20" style="11" customWidth="1"/>
     <col min="7" max="7" width="17" style="11" customWidth="1"/>
-    <col min="8" max="8" width="26" style="11" customWidth="1"/>
-    <col min="9" max="9" width="26" style="11" customWidth="1"/>
-    <col min="10" max="10" width="14" style="11" customWidth="1"/>
+    <col min="8" max="8" width="16" style="11" customWidth="1"/>
+    <col min="9" max="9" width="17" style="11" customWidth="1"/>
+    <col min="10" max="10" width="17" style="11" customWidth="1"/>
+    <col min="11" max="11" width="19" style="11" customWidth="1"/>
+    <col min="12" max="12" width="21" style="11" customWidth="1"/>
+    <col min="13" max="13" width="18" style="11" customWidth="1"/>
+    <col min="14" max="14" width="20" style="11" customWidth="1"/>
+    <col min="15" max="15" width="23" style="11" customWidth="1"/>
+    <col min="16" max="16" width="14" style="11" customWidth="1"/>
+    <col min="17" max="17" width="26" style="11" customWidth="1"/>
+    <col min="18" max="18" width="19" style="11" customWidth="1"/>
+    <col min="19" max="19" width="35" style="11" customWidth="1"/>
+    <col min="20" max="20" width="19" style="11" customWidth="1"/>
+    <col min="21" max="21" width="23" style="11" customWidth="1"/>
+    <col min="22" max="22" width="26" style="11" customWidth="1"/>
+    <col min="23" max="23" width="19" style="11" customWidth="1"/>
+    <col min="24" max="24" width="14" style="11" customWidth="1"/>
+    <col min="25" max="25" width="21" style="11" customWidth="1"/>
+    <col min="26" max="26" width="27" style="11" customWidth="1"/>
+    <col min="27" max="27" width="22" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="20" customHeight="1">
+    <row r="1" spans="1:27" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>277</v>
+        <v>619</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>248</v>
+        <v>588</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>278</v>
+        <v>620</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>279</v>
+        <v>621</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>280</v>
+        <v>622</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>281</v>
+        <v>623</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>282</v>
+        <v>624</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>283</v>
+        <v>625</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>284</v>
+        <v>626</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>285</v>
+        <v>627</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="S1" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="V1" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="W1" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="X1" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="Y1" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="Z1" s="8" t="s">
+        <v>681</v>
+      </c>
+      <c r="AA1" s="8" t="s">
+        <v>682</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>286</v>
+        <v>683</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>287</v>
+        <v>654</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>288</v>
+        <v>534</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>191</v>
-      </c>
+        <v>522</v>
+      </c>
+      <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>290</v>
+        <v>655</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>291</v>
+        <v>656</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>292</v>
+        <v>657</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>293</v>
+        <v>684</v>
       </c>
       <c r="J2" s="9"/>
+      <c r="K2" s="9" t="s">
+        <v>685</v>
+      </c>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="Y2" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="Z2" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="AA2" s="9"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="E2:E5000">
-      <formula1>Lists!$D$2:$D$3</formula1>
+  <dataValidations count="9">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="C2:C5000">
+      <formula1>Lists!$E$2:$E$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="D2:D5000">
+      <formula1>Lists!$U$2:$U$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="M2:M5000">
+      <formula1>Lists!$B$2:$B$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="N2:N5000">
+      <formula1>Lists!$C$2:$C$6</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="P2:P5000">
+      <formula1>Lists!$F$2:$F$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="Q2:Q5000">
+      <formula1>Lists!$G$2:$G$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="R2:R5000">
+      <formula1>Lists!$H$2:$H$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="U2:U5000">
+      <formula1>Lists!$N$2:$N$6</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="X2:X5000">
+      <formula1>Lists!$L$2:$L$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2529,42 +7046,623 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18" style="11" customWidth="1"/>
-    <col min="2" max="2" width="18" style="11" customWidth="1"/>
+    <col min="1" max="1" width="19" style="11" customWidth="1"/>
+    <col min="2" max="2" width="17" style="11" customWidth="1"/>
     <col min="3" max="3" width="14" style="11" customWidth="1"/>
     <col min="4" max="4" width="14" style="11" customWidth="1"/>
+    <col min="5" max="5" width="18" style="11" customWidth="1"/>
+    <col min="6" max="6" width="20" style="11" customWidth="1"/>
+    <col min="7" max="7" width="17" style="11" customWidth="1"/>
+    <col min="8" max="8" width="16" style="11" customWidth="1"/>
+    <col min="9" max="9" width="17" style="11" customWidth="1"/>
+    <col min="10" max="10" width="17" style="11" customWidth="1"/>
+    <col min="11" max="11" width="19" style="11" customWidth="1"/>
+    <col min="12" max="12" width="21" style="11" customWidth="1"/>
+    <col min="13" max="13" width="18" style="11" customWidth="1"/>
+    <col min="14" max="14" width="20" style="11" customWidth="1"/>
+    <col min="15" max="15" width="23" style="11" customWidth="1"/>
+    <col min="16" max="16" width="14" style="11" customWidth="1"/>
+    <col min="17" max="17" width="26" style="11" customWidth="1"/>
+    <col min="18" max="18" width="19" style="11" customWidth="1"/>
+    <col min="19" max="19" width="35" style="11" customWidth="1"/>
+    <col min="20" max="20" width="19" style="11" customWidth="1"/>
+    <col min="21" max="21" width="23" style="11" customWidth="1"/>
+    <col min="22" max="22" width="26" style="11" customWidth="1"/>
+    <col min="23" max="23" width="19" style="11" customWidth="1"/>
+    <col min="24" max="24" width="19" style="11" customWidth="1"/>
+    <col min="25" max="25" width="29" style="11" customWidth="1"/>
+    <col min="26" max="26" width="17" style="11" customWidth="1"/>
+    <col min="27" max="27" width="25" style="11" customWidth="1"/>
+    <col min="28" max="28" width="23" style="11" customWidth="1"/>
+    <col min="29" max="29" width="15" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="20" customHeight="1">
+    <row r="1" spans="1:29" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>294</v>
+        <v>619</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>295</v>
+        <v>588</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>296</v>
+        <v>620</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>297</v>
+        <v>621</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="S1" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="V1" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="W1" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="X1" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="Y1" s="8" t="s">
+        <v>690</v>
+      </c>
+      <c r="Z1" s="8" t="s">
+        <v>691</v>
+      </c>
+      <c r="AA1" s="8" t="s">
+        <v>692</v>
+      </c>
+      <c r="AB1" s="8" t="s">
+        <v>693</v>
+      </c>
+      <c r="AC1" s="8" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>298</v>
+        <v>695</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>299</v>
+        <v>654</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="D2" s="9"/>
+        <v>534</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>656</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>657</v>
+      </c>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="Z2" s="9" t="s">
+        <v>697</v>
+      </c>
+      <c r="AA2" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="AB2" s="9" t="s">
+        <v>657</v>
+      </c>
+      <c r="AC2" s="9"/>
     </row>
   </sheetData>
+  <dataValidations count="8">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="C2:C5000">
+      <formula1>Lists!$E$2:$E$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="D2:D5000">
+      <formula1>Lists!$V$2:$V$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="M2:M5000">
+      <formula1>Lists!$B$2:$B$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="N2:N5000">
+      <formula1>Lists!$C$2:$C$6</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="P2:P5000">
+      <formula1>Lists!$F$2:$F$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="Q2:Q5000">
+      <formula1>Lists!$G$2:$G$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="R2:R5000">
+      <formula1>Lists!$H$2:$H$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="U2:U5000">
+      <formula1>Lists!$N$2:$N$6</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AB2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19" style="11" customWidth="1"/>
+    <col min="2" max="2" width="17" style="11" customWidth="1"/>
+    <col min="3" max="3" width="14" style="11" customWidth="1"/>
+    <col min="4" max="4" width="14" style="11" customWidth="1"/>
+    <col min="5" max="5" width="18" style="11" customWidth="1"/>
+    <col min="6" max="6" width="20" style="11" customWidth="1"/>
+    <col min="7" max="7" width="17" style="11" customWidth="1"/>
+    <col min="8" max="8" width="16" style="11" customWidth="1"/>
+    <col min="9" max="9" width="17" style="11" customWidth="1"/>
+    <col min="10" max="10" width="17" style="11" customWidth="1"/>
+    <col min="11" max="11" width="19" style="11" customWidth="1"/>
+    <col min="12" max="12" width="21" style="11" customWidth="1"/>
+    <col min="13" max="13" width="18" style="11" customWidth="1"/>
+    <col min="14" max="14" width="20" style="11" customWidth="1"/>
+    <col min="15" max="15" width="23" style="11" customWidth="1"/>
+    <col min="16" max="16" width="14" style="11" customWidth="1"/>
+    <col min="17" max="17" width="26" style="11" customWidth="1"/>
+    <col min="18" max="18" width="19" style="11" customWidth="1"/>
+    <col min="19" max="19" width="35" style="11" customWidth="1"/>
+    <col min="20" max="20" width="19" style="11" customWidth="1"/>
+    <col min="21" max="21" width="23" style="11" customWidth="1"/>
+    <col min="22" max="22" width="26" style="11" customWidth="1"/>
+    <col min="23" max="23" width="19" style="11" customWidth="1"/>
+    <col min="24" max="24" width="24" style="11" customWidth="1"/>
+    <col min="25" max="25" width="17" style="11" customWidth="1"/>
+    <col min="26" max="26" width="18" style="11" customWidth="1"/>
+    <col min="27" max="27" width="16" style="11" customWidth="1"/>
+    <col min="28" max="28" width="16" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>588</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="S1" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="V1" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="W1" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="X1" s="8" t="s">
+        <v>699</v>
+      </c>
+      <c r="Y1" s="8" t="s">
+        <v>700</v>
+      </c>
+      <c r="Z1" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="AA1" s="8" t="s">
+        <v>702</v>
+      </c>
+      <c r="AB1" s="8" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>656</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>657</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>705</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9" t="s">
+        <v>706</v>
+      </c>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="V2" s="9" t="s">
+        <v>707</v>
+      </c>
+      <c r="W2" s="9" t="s">
+        <v>708</v>
+      </c>
+      <c r="X2" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="Y2" s="9" t="s">
+        <v>709</v>
+      </c>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+    </row>
+  </sheetData>
+  <dataValidations count="9">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="C2:C5000">
+      <formula1>Lists!$E$2:$E$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="D2:D5000">
+      <formula1>Lists!$W$2:$W$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="M2:M5000">
+      <formula1>Lists!$B$2:$B$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="N2:N5000">
+      <formula1>Lists!$C$2:$C$6</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="P2:P5000">
+      <formula1>Lists!$F$2:$F$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="Q2:Q5000">
+      <formula1>Lists!$G$2:$G$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="R2:R5000">
+      <formula1>Lists!$H$2:$H$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="U2:U5000">
+      <formula1>Lists!$N$2:$N$6</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="X2:X5000">
+      <formula1>Lists!$M$2:$M$4</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:W2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19" style="11" customWidth="1"/>
+    <col min="2" max="2" width="17" style="11" customWidth="1"/>
+    <col min="3" max="3" width="14" style="11" customWidth="1"/>
+    <col min="4" max="4" width="14" style="11" customWidth="1"/>
+    <col min="5" max="5" width="18" style="11" customWidth="1"/>
+    <col min="6" max="6" width="20" style="11" customWidth="1"/>
+    <col min="7" max="7" width="17" style="11" customWidth="1"/>
+    <col min="8" max="8" width="16" style="11" customWidth="1"/>
+    <col min="9" max="9" width="17" style="11" customWidth="1"/>
+    <col min="10" max="10" width="17" style="11" customWidth="1"/>
+    <col min="11" max="11" width="19" style="11" customWidth="1"/>
+    <col min="12" max="12" width="21" style="11" customWidth="1"/>
+    <col min="13" max="13" width="18" style="11" customWidth="1"/>
+    <col min="14" max="14" width="20" style="11" customWidth="1"/>
+    <col min="15" max="15" width="23" style="11" customWidth="1"/>
+    <col min="16" max="16" width="14" style="11" customWidth="1"/>
+    <col min="17" max="17" width="26" style="11" customWidth="1"/>
+    <col min="18" max="18" width="19" style="11" customWidth="1"/>
+    <col min="19" max="19" width="35" style="11" customWidth="1"/>
+    <col min="20" max="20" width="19" style="11" customWidth="1"/>
+    <col min="21" max="21" width="23" style="11" customWidth="1"/>
+    <col min="22" max="22" width="26" style="11" customWidth="1"/>
+    <col min="23" max="23" width="19" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>588</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="S1" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="V1" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="W1" s="8" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>710</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>656</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>657</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>707</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9" t="s">
+        <v>711</v>
+      </c>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+    </row>
+  </sheetData>
+  <dataValidations count="8">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="C2:C5000">
+      <formula1>Lists!$E$2:$E$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="D2:D5000">
+      <formula1>Lists!$X$2:$X$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="M2:M5000">
+      <formula1>Lists!$B$2:$B$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="N2:N5000">
+      <formula1>Lists!$C$2:$C$6</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="P2:P5000">
+      <formula1>Lists!$F$2:$F$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="Q2:Q5000">
+      <formula1>Lists!$G$2:$G$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="R2:R5000">
+      <formula1>Lists!$H$2:$H$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="U2:U5000">
+      <formula1>Lists!$N$2:$N$6</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/package/05_Delivery/Upload_Templates/GoLive_Migration_Workbook.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/GoLive_Migration_Workbook.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="291">
   <si>
     <t xml:space="preserve">Item</t>
   </si>
@@ -577,7 +577,7 @@
     <t xml:space="preserve">registered</t>
   </si>
   <si>
-    <t xml:space="preserve">APEX</t>
+    <t xml:space="preserve">AXA</t>
   </si>
   <si>
     <t xml:space="preserve">CL-COMP</t>
@@ -595,7 +595,7 @@
     <t xml:space="preserve">in-review</t>
   </si>
   <si>
-    <t xml:space="preserve">AXA</t>
+    <t xml:space="preserve">MAAGAP</t>
   </si>
   <si>
     <t xml:space="preserve">CL-VOL</t>
@@ -604,7 +604,7 @@
     <t xml:space="preserve">Partial</t>
   </si>
   <si>
-    <t xml:space="preserve">EVERSAFE</t>
+    <t xml:space="preserve">MALAYAN</t>
   </si>
   <si>
     <t xml:space="preserve">CTPL</t>
@@ -613,7 +613,7 @@
     <t xml:space="preserve">Completed</t>
   </si>
   <si>
-    <t xml:space="preserve">FPG</t>
+    <t xml:space="preserve">PIONEER</t>
   </si>
   <si>
     <t xml:space="preserve">GPA</t>
@@ -622,52 +622,22 @@
     <t xml:space="preserve">Refunded</t>
   </si>
   <si>
-    <t xml:space="preserve">GOLDENHORIZON</t>
+    <t xml:space="preserve">STANDARD</t>
   </si>
   <si>
     <t xml:space="preserve">MOTOR</t>
   </si>
   <si>
-    <t xml:space="preserve">INTEGRITY</t>
+    <t xml:space="preserve">STRONGHOLD</t>
   </si>
   <si>
     <t xml:space="preserve">PA</t>
   </si>
   <si>
-    <t xml:space="preserve">LIBERTYSHIELD</t>
-  </si>
-  <si>
     <t xml:space="preserve">PARCEL</t>
   </si>
   <si>
-    <t xml:space="preserve">MAAGAP</t>
-  </si>
-  <si>
     <t xml:space="preserve">TRAVEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MALAYAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPFRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MERCANTILE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIONEER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SECUREGUARD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SENTINEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STANDARD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STRONGHOLD</t>
   </si>
   <si>
     <t xml:space="preserve">Client Code *</t>
@@ -927,7 +897,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -1881,7 +1851,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" style="11" customWidth="1"/>
@@ -2011,11 +1981,9 @@
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="11"/>
+      <c r="F8" s="11" t="s">
         <v>205</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="9">
@@ -2023,92 +1991,10 @@
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
-      <c r="E9" s="11" t="s">
-        <v>207</v>
-      </c>
+      <c r="E9" s="11"/>
       <c r="F9" s="11" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="F10" s="11"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="F11" s="11"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="F12" s="11"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="F13" s="11"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="F14" s="11"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="F15" s="11"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="F16" s="11"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="F17" s="11"/>
+        <v>206</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2141,104 +2027,104 @@
   <sheetData>
     <row r="1" spans="1:17" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="K1" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>223</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="P1" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>182</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="9" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -2276,40 +2162,40 @@
   <sheetData>
     <row r="1" spans="1:16" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="L1" s="8" t="s">
         <v>248</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>258</v>
       </c>
       <c r="M1" s="8" t="s">
         <v>177</v>
@@ -2318,43 +2204,43 @@
         <v>178</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>202</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
@@ -2364,14 +2250,14 @@
         <v>197</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="P2" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="C2:C5000">
-      <formula1>Lists!$E$2:$E$17</formula1>
+      <formula1>Lists!$E$2:$E$7</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="D2:D5000">
       <formula1>Lists!$F$2:$F$9</formula1>
@@ -2401,36 +2287,36 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -2457,63 +2343,63 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>191</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="J2" s="9"/>
     </row>
@@ -2540,27 +2426,27 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="D2" s="9"/>
     </row>

--- a/docs/package/05_Delivery/Upload_Templates/GoLive_Migration_Workbook.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/GoLive_Migration_Workbook.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="787">
   <si>
     <t xml:space="preserve">Item</t>
   </si>
@@ -105,13 +105,13 @@
     <t xml:space="preserve">1. Clients</t>
   </si>
   <si>
-    <t xml:space="preserve">Operations &gt; Clients. Key: Client Code</t>
+    <t xml:space="preserve">Policy Servicing &gt; Clients. Key: Client Code</t>
   </si>
   <si>
     <t xml:space="preserve">2. Policies - Motor</t>
   </si>
   <si>
-    <t xml:space="preserve">Operations &gt; Policy. Key: Policy Number. After: Clients</t>
+    <t xml:space="preserve">Policy Servicing &gt; Policy. Key: Policy Number. After: Clients</t>
   </si>
   <si>
     <t xml:space="preserve">3. Policies - CTPL</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">10. Open Claims</t>
   </si>
   <si>
-    <t xml:space="preserve">Operations &gt; Claims. Key: Claim Number. After: Policies - Motor, Policies - CTPL, Policies - Personal Accident, Policies - Credit Life, Policies - Travel, Policies - Other Lines</t>
+    <t xml:space="preserve">Policy Servicing &gt; Claims. Key: Claim Number. After: Policies - Motor, Policies - CTPL, Policies - Personal Accident, Policies - Credit Life, Policies - Travel, Policies - Other Lines</t>
   </si>
   <si>
     <t xml:space="preserve">11. Opening Balances</t>
@@ -456,7 +456,7 @@
     <t xml:space="preserve">Leads and quotations in progress</t>
   </si>
   <si>
-    <t xml:space="preserve">Operations &gt; Sales &amp; Marketing &gt; Prospects / Quotations &gt; Bulk Upload</t>
+    <t xml:space="preserve">Sales &amp; Placement &gt; Prospects / Quotations &gt; Bulk Upload</t>
   </si>
   <si>
     <t xml:space="preserve">Unreconciled bank items</t>
@@ -1569,150 +1569,153 @@
     <t xml:space="preserve">in-review</t>
   </si>
   <si>
+    <t xml:space="preserve">CTINS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAL-ALB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renewal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">motorcycles_tricycles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRV-ANN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gross premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CL-VOL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial</t>
+  </si>
+  <si>
     <t xml:space="preserve">MAAGAP</t>
   </si>
   <si>
-    <t xml:space="preserve">DAV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAL-ALB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renewal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Honda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">motorcycles_tricycles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRV-ANN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Policies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gross premium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CL-VOL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partial</t>
+    <t xml:space="preserve">HO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hyundai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">private_cars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRV-REN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">net premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completed</t>
   </si>
   <si>
     <t xml:space="preserve">MALAYAN</t>
   </si>
   <si>
-    <t xml:space="preserve">HO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hyundai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">private_cars</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRV-REN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Items</t>
-  </si>
-  <si>
-    <t xml:space="preserve">net premium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Completed</t>
+    <t xml:space="preserve">TCB-CEB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isuzu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-Dated Cheques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sum insured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refunded</t>
   </si>
   <si>
     <t xml:space="preserve">PIONEER</t>
   </si>
   <si>
-    <t xml:space="preserve">TCB-CEB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isuzu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BPI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post-Dated Cheques</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sum insured</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Refunded</t>
+    <t xml:space="preserve">TFS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitsubishi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Claims</t>
+  </si>
+  <si>
+    <t xml:space="preserve">original amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORCR</t>
   </si>
   <si>
     <t xml:space="preserve">STANDARD</t>
   </si>
   <si>
-    <t xml:space="preserve">TFS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitsubishi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CBC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Claims</t>
-  </si>
-  <si>
-    <t xml:space="preserve">original amount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ORCR</t>
+    <t xml:space="preserve">TFS-CEB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nissan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opening Balances</t>
+  </si>
+  <si>
+    <t xml:space="preserve">open balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOAN</t>
   </si>
   <si>
     <t xml:space="preserve">STRONGHOLD</t>
   </si>
   <si>
-    <t xml:space="preserve">TFS-CEB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nissan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DBP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opening Balances</t>
-  </si>
-  <si>
-    <t xml:space="preserve">open balance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOAN</t>
-  </si>
-  <si>
     <t xml:space="preserve">TFS-HQ</t>
   </si>
   <si>
@@ -2379,7 +2382,7 @@
     <t xml:space="preserve">Generated at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-11T04:55:40.599Z</t>
+    <t xml:space="preserve">2026-10-12T02:03:01.137Z</t>
   </si>
   <si>
     <t xml:space="preserve">Generated by</t>
@@ -5063,39 +5066,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -5127,57 +5130,57 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I2" s="9"/>
     </row>
@@ -5210,63 +5213,63 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>513</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="J2" s="9"/>
     </row>
@@ -5293,27 +5296,27 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D2" s="9"/>
     </row>
@@ -5335,21 +5338,21 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>524</v>
@@ -5358,7 +5361,7 @@
         <v>504</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
   </sheetData>
@@ -5388,36 +5391,36 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="6">
@@ -5425,20 +5428,20 @@
         <v>3</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
   </sheetData>
@@ -5863,14 +5866,16 @@
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
+      <c r="E8" s="11" t="s">
+        <v>562</v>
+      </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H8" s="11"/>
       <c r="I8" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="J8" s="11"/>
       <c r="K8" s="11"/>
@@ -5878,16 +5883,16 @@
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
       <c r="O8" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="Q8" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="R8" s="11" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="S8" s="11"/>
       <c r="T8" s="11"/>
@@ -5904,11 +5909,11 @@
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="11" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H9" s="11"/>
       <c r="I9" s="11" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
@@ -5916,14 +5921,14 @@
       <c r="M9" s="11"/>
       <c r="N9" s="11"/>
       <c r="O9" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="P9" s="11"/>
       <c r="Q9" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="R9" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="S9" s="11"/>
       <c r="T9" s="11"/>
@@ -5940,7 +5945,7 @@
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -5950,14 +5955,14 @@
       <c r="M10" s="11"/>
       <c r="N10" s="11"/>
       <c r="O10" s="11" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="P10" s="11"/>
       <c r="Q10" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="R10" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="S10" s="11"/>
       <c r="T10" s="11"/>
@@ -5974,7 +5979,7 @@
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
@@ -5984,14 +5989,14 @@
       <c r="M11" s="11"/>
       <c r="N11" s="11"/>
       <c r="O11" s="11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="P11" s="11"/>
       <c r="Q11" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="R11" s="11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="S11" s="11"/>
       <c r="T11" s="11"/>
@@ -6008,7 +6013,7 @@
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="11" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
@@ -6018,14 +6023,14 @@
       <c r="M12" s="11"/>
       <c r="N12" s="11"/>
       <c r="O12" s="11" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="P12" s="11"/>
       <c r="Q12" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="R12" s="11" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S12" s="11"/>
       <c r="T12" s="11"/>
@@ -6042,7 +6047,7 @@
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="11" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
@@ -6052,14 +6057,14 @@
       <c r="M13" s="11"/>
       <c r="N13" s="11"/>
       <c r="O13" s="11" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="P13" s="11"/>
       <c r="Q13" s="11" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="R13" s="11" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="S13" s="11"/>
       <c r="T13" s="11"/>
@@ -6076,7 +6081,7 @@
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
@@ -6086,11 +6091,11 @@
       <c r="M14" s="11"/>
       <c r="N14" s="11"/>
       <c r="O14" s="11" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="P14" s="11"/>
       <c r="Q14" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="R14" s="11"/>
       <c r="S14" s="11"/>
@@ -6116,11 +6121,11 @@
       <c r="M15" s="11"/>
       <c r="N15" s="11"/>
       <c r="O15" s="11" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="P15" s="11"/>
       <c r="Q15" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="R15" s="11"/>
       <c r="S15" s="11"/>
@@ -6146,11 +6151,11 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
       <c r="O16" s="11" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="P16" s="11"/>
       <c r="Q16" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="R16" s="11"/>
       <c r="S16" s="11"/>
@@ -6176,11 +6181,11 @@
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
       <c r="O17" s="11" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="P17" s="11"/>
       <c r="Q17" s="11" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="R17" s="11"/>
       <c r="S17" s="11"/>
@@ -6206,7 +6211,7 @@
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
       <c r="O18" s="11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="P18" s="11"/>
       <c r="Q18" s="11"/>
@@ -6249,104 +6254,104 @@
   <sheetData>
     <row r="1" spans="1:17" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>487</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="9" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
   </sheetData>
@@ -6406,40 +6411,40 @@
   <sheetData>
     <row r="1" spans="1:38" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M1" s="8" t="s">
         <v>464</v>
@@ -6448,109 +6453,109 @@
         <v>465</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="R1" s="8" t="s">
         <v>470</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="W1" s="8" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="X1" s="8" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="Y1" s="8" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AB1" s="8" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AC1" s="8" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AD1" s="8" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AE1" s="8" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AF1" s="8" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG1" s="8" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AH1" s="8" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AI1" s="8" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AJ1" s="8" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AK1" s="8" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AL1" s="8" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>504</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
@@ -6573,43 +6578,43 @@
       <c r="V2" s="9"/>
       <c r="W2" s="9"/>
       <c r="X2" s="9" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="Y2" s="9"/>
       <c r="Z2" s="9" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AA2" s="9"/>
       <c r="AB2" s="9"/>
       <c r="AC2" s="9" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AD2" s="9" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AE2" s="9" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AF2" s="9" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AG2" s="9"/>
       <c r="AH2" s="9"/>
       <c r="AI2" s="9" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AJ2" s="9" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AK2" s="9" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AL2" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="10">
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="C2:C5000">
-      <formula1>Lists!$E$2:$E$7</formula1>
+      <formula1>Lists!$E$2:$E$8</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="D2:D5000">
       <formula1>Lists!$S$2:$S$2</formula1>
@@ -6685,40 +6690,40 @@
   <sheetData>
     <row r="1" spans="1:33" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M1" s="8" t="s">
         <v>464</v>
@@ -6727,92 +6732,92 @@
         <v>465</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="R1" s="8" t="s">
         <v>470</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="W1" s="8" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="X1" s="8" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="Y1" s="8" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AB1" s="8" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AC1" s="8" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AD1" s="8" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AE1" s="8" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AF1" s="8" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AG1" s="8" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>505</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="9" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
@@ -6835,20 +6840,20 @@
       <c r="V2" s="9"/>
       <c r="W2" s="9"/>
       <c r="X2" s="9" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
       <c r="AA2" s="9"/>
       <c r="AB2" s="9"/>
       <c r="AC2" s="9" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AD2" s="9" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AE2" s="9" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AF2" s="9"/>
       <c r="AG2" s="9"/>
@@ -6856,7 +6861,7 @@
   </sheetData>
   <dataValidations count="10">
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="C2:C5000">
-      <formula1>Lists!$E$2:$E$7</formula1>
+      <formula1>Lists!$E$2:$E$8</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="D2:D5000">
       <formula1>Lists!$T$2:$T$2</formula1>
@@ -6926,40 +6931,40 @@
   <sheetData>
     <row r="1" spans="1:27" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M1" s="8" t="s">
         <v>464</v>
@@ -6968,74 +6973,74 @@
         <v>465</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="R1" s="8" t="s">
         <v>470</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="W1" s="8" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="X1" s="8" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="Y1" s="8" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>526</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="9" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
@@ -7058,20 +7063,20 @@
       <c r="V2" s="9"/>
       <c r="W2" s="9"/>
       <c r="X2" s="9" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="Y2" s="9" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="Z2" s="9" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AA2" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="9">
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="C2:C5000">
-      <formula1>Lists!$E$2:$E$7</formula1>
+      <formula1>Lists!$E$2:$E$8</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="D2:D5000">
       <formula1>Lists!$U$2:$U$3</formula1>
@@ -7140,40 +7145,40 @@
   <sheetData>
     <row r="1" spans="1:29" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M1" s="8" t="s">
         <v>464</v>
@@ -7182,78 +7187,78 @@
         <v>465</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="R1" s="8" t="s">
         <v>470</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="W1" s="8" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="X1" s="8" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="Y1" s="8" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AB1" s="8" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AC1" s="8" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>507</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
       <c r="K2" s="9" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
@@ -7277,23 +7282,23 @@
       <c r="W2" s="9"/>
       <c r="X2" s="9"/>
       <c r="Y2" s="9" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="Z2" s="9" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AA2" s="9" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AB2" s="9" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AC2" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="8">
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="C2:C5000">
-      <formula1>Lists!$E$2:$E$7</formula1>
+      <formula1>Lists!$E$2:$E$8</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="D2:D5000">
       <formula1>Lists!$V$2:$V$3</formula1>
@@ -7358,40 +7363,40 @@
   <sheetData>
     <row r="1" spans="1:28" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M1" s="8" t="s">
         <v>464</v>
@@ -7400,77 +7405,77 @@
         <v>465</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="R1" s="8" t="s">
         <v>470</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="W1" s="8" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="X1" s="8" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="Y1" s="8" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AB1" s="8" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>508</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="9" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
@@ -7490,19 +7495,19 @@
       <c r="S2" s="9"/>
       <c r="T2" s="9"/>
       <c r="U2" s="9" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="V2" s="9" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="W2" s="9" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="X2" s="9" t="s">
         <v>521</v>
       </c>
       <c r="Y2" s="9" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="Z2" s="9"/>
       <c r="AA2" s="9"/>
@@ -7511,7 +7516,7 @@
   </sheetData>
   <dataValidations count="9">
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="C2:C5000">
-      <formula1>Lists!$E$2:$E$7</formula1>
+      <formula1>Lists!$E$2:$E$8</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="D2:D5000">
       <formula1>Lists!$W$2:$W$2</formula1>
@@ -7574,40 +7579,40 @@
   <sheetData>
     <row r="1" spans="1:23" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M1" s="8" t="s">
         <v>464</v>
@@ -7616,62 +7621,62 @@
         <v>465</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="R1" s="8" t="s">
         <v>470</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="W1" s="8" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>509</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="9" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
@@ -7697,7 +7702,7 @@
   </sheetData>
   <dataValidations count="8">
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="C2:C5000">
-      <formula1>Lists!$E$2:$E$7</formula1>
+      <formula1>Lists!$E$2:$E$8</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="D2:D5000">
       <formula1>Lists!$X$2:$X$2</formula1>
